--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -866,7 +866,7 @@
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.3</v>
@@ -1634,7 +1634,7 @@
         <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>FK Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2901,29 +2901,29 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.01</v>
       </c>
-      <c r="K10" t="n">
-        <v>950</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,49 +3134,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vasteras SK</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.3</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FK Kyzyl-Zhar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Vasteras SK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,31 +4404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>1.54</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>2.16</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>1.86</v>
       </c>
       <c r="K22" t="n">
         <v>4.4</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I23" t="n">
         <v>2.14</v>
@@ -6206,7 +6206,7 @@
         <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -866,7 +866,7 @@
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
         <v>1.74</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
@@ -1634,7 +1634,7 @@
         <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
         <v>3.95</v>
@@ -1906,7 +1906,7 @@
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
         <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3155,10 +3155,10 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G12" t="n">
         <v>3.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
         <v>2.7</v>
@@ -3666,7 +3666,7 @@
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
         <v>1.35</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>2.16</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.86</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
         <v>4.4</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="n">
         <v>1.91</v>
@@ -6203,10 +6203,10 @@
         <v>2.14</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -890,7 +890,7 @@
         <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H3" t="n">
         <v>3.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1374,13 +1374,13 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1652,7 +1652,7 @@
         <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
         <v>2.42</v>
@@ -1885,10 +1885,10 @@
         <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>2.36</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
         <v>1.84</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>1.46</v>
@@ -3917,10 +3917,10 @@
         <v>1.54</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4951,16 +4951,16 @@
         <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="n">
         <v>3.5</v>
@@ -5444,7 +5444,7 @@
         <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5946,10 +5946,10 @@
         <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
         <v>4.4</v>
@@ -5967,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
         <v>1.64</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
         <v>1.74</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB47"/>
+  <dimension ref="A1:CB50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,28 +860,28 @@
         <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="H2" t="n">
         <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.43</v>
@@ -890,13 +890,13 @@
         <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.96</v>
@@ -905,182 +905,182 @@
         <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1120,19 +1120,19 @@
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
         <v>2.72</v>
@@ -1141,7 +1141,7 @@
         <v>1.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -1150,52 +1150,52 @@
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>80</v>
@@ -1207,70 +1207,70 @@
         <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>32</v>
       </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
         <v>1.87</v>
@@ -1383,7 +1383,7 @@
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1395,10 +1395,10 @@
         <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
@@ -1407,10 +1407,10 @@
         <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1434,7 +1434,7 @@
         <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>26</v>
@@ -1461,28 +1461,28 @@
         <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO4" t="n">
         <v>160</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1494,7 +1494,7 @@
         <v>18.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>9</v>
@@ -1506,25 +1506,25 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.05</v>
@@ -1554,7 +1554,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
         <v>34</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
         <v>3.55</v>
@@ -1631,7 +1631,7 @@
         <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>3.35</v>
@@ -1652,7 +1652,7 @@
         <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
@@ -1664,13 +1664,13 @@
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
         <v>11</v>
@@ -1688,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
         <v>18.5</v>
@@ -1700,7 +1700,7 @@
         <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1730,13 +1730,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1745,40 +1745,40 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX5" t="n">
         <v>12</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD5" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.82</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1978,28 +1978,28 @@
         <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>20</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW6" t="n">
         <v>13.5</v>
@@ -2014,13 +2014,13 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
         <v>4.1</v>
@@ -2029,7 +2029,7 @@
         <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
         <v>6.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
         <v>1.75</v>
@@ -2214,7 +2214,7 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
         <v>150</v>
@@ -2235,64 +2235,64 @@
         <v>14.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4</v>
       </c>
       <c r="BD7" t="n">
         <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
         <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="n">
         <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
         <v>4.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -2408,13 +2408,13 @@
         <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
@@ -2429,10 +2429,10 @@
         <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2489,10 +2489,10 @@
         <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>4.9</v>
@@ -2501,34 +2501,34 @@
         <v>5.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
         <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
         <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>4.9</v>
@@ -2537,7 +2537,7 @@
         <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BG8" t="n">
         <v>5.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
@@ -2659,22 +2659,22 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
         <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
@@ -2683,10 +2683,10 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2698,13 +2698,13 @@
         <v>17.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
@@ -2716,7 +2716,7 @@
         <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
@@ -2731,7 +2731,7 @@
         <v>48</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>140</v>
@@ -2746,28 +2746,28 @@
         <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>3.95</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2776,22 +2776,22 @@
         <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
         <v>2.36</v>
@@ -2922,16 +2922,16 @@
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -2958,7 +2958,7 @@
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>19</v>
@@ -2997,40 +2997,40 @@
         <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -3039,16 +3039,16 @@
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
         <v>14.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H11" t="n">
         <v>2.38</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J11" t="n">
         <v>3.55</v>
@@ -3167,7 +3167,7 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.25</v>
@@ -3185,13 +3185,13 @@
         <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
         <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W11" t="n">
         <v>1.44</v>
@@ -3209,10 +3209,10 @@
         <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>12.5</v>
@@ -3224,16 +3224,16 @@
         <v>27</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
         <v>38</v>
@@ -3242,13 +3242,13 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
         <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP11" t="n">
         <v>15.5</v>
@@ -3269,7 +3269,7 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
@@ -3281,7 +3281,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
         <v>4.8</v>
@@ -3296,7 +3296,7 @@
         <v>4.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
         <v>19</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
@@ -3430,13 +3430,13 @@
         <v>1.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3678,7 +3678,7 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
@@ -3699,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="G14" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.7</v>
       </c>
-      <c r="I14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
         <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.63</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.98</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP15" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="H16" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.39</v>
@@ -4437,148 +4437,148 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
         <v>46</v>
       </c>
       <c r="AF16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH16" t="n">
         <v>22</v>
       </c>
-      <c r="AG16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
         <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="AW16" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="AY16" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4667,172 +4667,172 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>1.56</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
         <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17" t="n">
         <v>12.5</v>
@@ -4844,19 +4844,19 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4865,16 +4865,16 @@
         <v>2.58</v>
       </c>
       <c r="BT17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BU17" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BV17" t="n">
         <v>10.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX17" t="n">
         <v>30</v>
@@ -4883,14 +4883,14 @@
         <v>2.44</v>
       </c>
       <c r="BZ17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.36</v>
+        <v>7.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4933,34 +4933,34 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.02</v>
       </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
@@ -5480,7 +5480,7 @@
         <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
         <v>46</v>
@@ -5492,10 +5492,10 @@
         <v>50</v>
       </c>
       <c r="AA20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="n">
         <v>13.5</v>
@@ -5522,7 +5522,7 @@
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -5531,7 +5531,7 @@
         <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -5546,7 +5546,7 @@
         <v>5.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT20" t="n">
         <v>12.5</v>
@@ -5555,7 +5555,7 @@
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AW20" t="n">
         <v>5.2</v>
@@ -5570,10 +5570,10 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
         <v>1.88</v>
@@ -5695,7 +5695,7 @@
         <v>5.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
         <v>4.4</v>
@@ -5713,7 +5713,7 @@
         <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
         <v>1.74</v>
@@ -5734,7 +5734,7 @@
         <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X21" t="n">
         <v>23</v>
@@ -5791,7 +5791,7 @@
         <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>14</v>
@@ -5809,31 +5809,31 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="AW21" t="n">
         <v>3.9</v>
       </c>
       <c r="AX21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY21" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY21" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="BA21" t="n">
         <v>3.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>3.45</v>
       </c>
       <c r="BD21" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="BE21" t="n">
         <v>4</v>
@@ -5848,7 +5848,7 @@
         <v>3.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.800000000000001</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,246 +5928,246 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>5.9</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FK Altay</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tobol Kostanay</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,229 +6436,229 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI24" t="n">
         <v>3.8</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="BJ24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN24" t="n">
+      <c r="BQ24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV24" t="n">
         <v>23</v>
       </c>
-      <c r="AO24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW24" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,246 +6690,246 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger FC</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shenzhen Peng City</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P25" t="n">
         <v>1.07</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q25" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>1.54</v>
       </c>
       <c r="T25" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,239 +6944,239 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>1.08</v>
+        <v>3.55</v>
       </c>
       <c r="O26" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.07</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>1.54</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7231,19 +7231,19 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" t="n">
         <v>1.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S27" t="n">
         <v>1.33</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,7 +7485,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.16</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7739,13 +7739,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="O29" t="n">
         <v>1.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Q29" t="n">
         <v>1.3</v>
@@ -7763,7 +7763,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -7975,10 +7975,10 @@
         <v>3.55</v>
       </c>
       <c r="H30" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I30" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J30" t="n">
         <v>3.55</v>
@@ -8005,7 +8005,7 @@
         <v>1.87</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
         <v>3.15</v>
@@ -8017,7 +8017,7 @@
         <v>2.26</v>
       </c>
       <c r="V30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W30" t="n">
         <v>1.39</v>
@@ -8029,13 +8029,13 @@
         <v>11</v>
       </c>
       <c r="Z30" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC30" t="n">
         <v>8.4</v>
@@ -8044,37 +8044,37 @@
         <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AF30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AI30" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AL30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN30" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AP30" t="n">
         <v>14</v>
@@ -8086,7 +8086,7 @@
         <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>12.5</v>
@@ -8110,22 +8110,22 @@
         <v>14.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB30" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>26</v>
+        <v>5.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BG30" t="n">
         <v>14.5</v>
@@ -8170,7 +8170,7 @@
         <v>5.3</v>
       </c>
       <c r="BU30" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BV30" t="n">
         <v>16.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -8229,16 +8229,16 @@
         <v>3.1</v>
       </c>
       <c r="H31" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
         <v>1.37</v>
@@ -8250,10 +8250,10 @@
         <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
         <v>1.87</v>
@@ -8271,7 +8271,7 @@
         <v>2.26</v>
       </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W31" t="n">
         <v>1.48</v>
@@ -8283,7 +8283,7 @@
         <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA31" t="n">
         <v>46</v>
@@ -8307,7 +8307,7 @@
         <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
         <v>46</v>
@@ -8325,7 +8325,7 @@
         <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -8340,7 +8340,7 @@
         <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -8352,7 +8352,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AX31" t="n">
         <v>17.5</v>
@@ -8364,25 +8364,25 @@
         <v>14</v>
       </c>
       <c r="BA31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE31" t="n">
         <v>6</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
         <v>19</v>
       </c>
       <c r="BG31" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="G32" t="n">
         <v>1.81</v>
@@ -8486,7 +8486,7 @@
         <v>4.9</v>
       </c>
       <c r="I32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
@@ -8507,22 +8507,22 @@
         <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R32" t="n">
         <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V32" t="n">
         <v>1.23</v>
@@ -8552,13 +8552,13 @@
         <v>25</v>
       </c>
       <c r="AE32" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
         <v>14</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
         <v>23</v>
@@ -8582,43 +8582,43 @@
         <v>10.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP32" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AT32" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
         <v>17</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
         <v>13.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BB32" t="n">
         <v>13</v>
@@ -8630,13 +8630,13 @@
         <v>21</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BH32" t="n">
         <v>4.1</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>2.08</v>
       </c>
       <c r="I33" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J33" t="n">
         <v>3.8</v>
@@ -8767,16 +8767,16 @@
         <v>1.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S33" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T33" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U33" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V33" t="n">
         <v>1.81</v>
@@ -8812,7 +8812,7 @@
         <v>34</v>
       </c>
       <c r="AG33" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH33" t="n">
         <v>19</v>
@@ -8824,10 +8824,10 @@
         <v>75</v>
       </c>
       <c r="AK33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL33" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM33" t="n">
         <v>75</v>
@@ -8839,10 +8839,10 @@
         <v>13.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AR33" t="n">
         <v>11.5</v>
@@ -8851,16 +8851,16 @@
         <v>19</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="AX33" t="n">
         <v>20</v>
@@ -8869,7 +8869,7 @@
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BA33" t="n">
         <v>20</v>
@@ -8881,7 +8881,7 @@
         <v>3.95</v>
       </c>
       <c r="BD33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE33" t="n">
         <v>4.1</v>
@@ -8890,7 +8890,7 @@
         <v>19</v>
       </c>
       <c r="BG33" t="n">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="BH33" t="n">
         <v>4.2</v>
@@ -8908,13 +8908,13 @@
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN33" t="n">
         <v>7.2</v>
       </c>
       <c r="BO33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
@@ -8926,7 +8926,7 @@
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT33" t="n">
         <v>5.3</v>
@@ -8938,7 +8938,7 @@
         <v>14</v>
       </c>
       <c r="BW33" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -9245,10 +9245,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I35" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J35" t="n">
         <v>5.1</v>
@@ -9287,10 +9287,10 @@
         <v>2.44</v>
       </c>
       <c r="V35" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="W35" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
         <v>44</v>
@@ -9347,7 +9347,7 @@
         <v>5.1</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
         <v>11.5</v>
@@ -9359,19 +9359,19 @@
         <v>11.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
         <v>10.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW35" t="n">
         <v>10.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
         <v>20</v>
@@ -9383,19 +9383,19 @@
         <v>18.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
         <v>3.6</v>
@@ -9410,31 +9410,31 @@
         <v>9.6</v>
       </c>
       <c r="BK35" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>50</v>
+        <v>2.5</v>
       </c>
       <c r="BN35" t="n">
         <v>11</v>
       </c>
       <c r="BO35" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>32</v>
+        <v>2.44</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>29</v>
+        <v>2.42</v>
       </c>
       <c r="BT35" t="n">
         <v>4.7</v>
@@ -9446,23 +9446,23 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BW35" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BZ35" t="n">
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -9505,208 +9505,208 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G37" t="n">
         <v>1.37</v>
@@ -9756,10 +9756,10 @@
         <v>10.5</v>
       </c>
       <c r="I37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K37" t="n">
         <v>6.4</v>
@@ -9777,25 +9777,25 @@
         <v>1.21</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q37" t="n">
         <v>1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T37" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U37" t="n">
         <v>1.86</v>
       </c>
       <c r="V37" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
         <v>3.7</v>
@@ -9816,7 +9816,7 @@
         <v>11</v>
       </c>
       <c r="AC37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD37" t="n">
         <v>46</v>
@@ -9828,7 +9828,7 @@
         <v>10</v>
       </c>
       <c r="AG37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH37" t="n">
         <v>34</v>
@@ -9849,7 +9849,7 @@
         <v>190</v>
       </c>
       <c r="AN37" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO37" t="n">
         <v>290</v>
@@ -9858,13 +9858,13 @@
         <v>18.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.5</v>
+        <v>28</v>
       </c>
       <c r="AR37" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT37" t="n">
         <v>8</v>
@@ -9873,10 +9873,10 @@
         <v>11</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX37" t="n">
         <v>6.8</v>
@@ -9885,34 +9885,34 @@
         <v>8.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC37" t="n">
         <v>10.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH37" t="n">
         <v>4.4</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ37" t="n">
         <v>13</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10025,22 +10025,22 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="O38" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S38" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10049,7 +10049,7 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10246,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -10267,225 +10267,225 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P39" t="n">
         <v>1.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10500,229 +10500,229 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P40" t="n">
-        <v>2.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
         <v>0</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10754,246 +10754,246 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V41" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11008,246 +11008,246 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P42" t="n">
-        <v>2.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11257,251 +11257,251 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J43" t="n">
         <v>3.75</v>
       </c>
-      <c r="G43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K43" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BI43" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN43" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR43" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS43" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BT43" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU43" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW43" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BX43" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA43" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11511,54 +11511,54 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P44" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -11748,14 +11748,14 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11765,51 +11765,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q45" t="n">
         <v>1.01</v>
@@ -12002,14 +12002,14 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12019,36 +12019,36 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -12273,17 +12273,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -12510,7 +12510,769 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB48" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:44:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB49" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:44:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB50" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
@@ -899,7 +899,7 @@
         <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
         <v>1.87</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,7 +1135,7 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
         <v>1.53</v>
@@ -1150,16 +1150,16 @@
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
         <v>1.44</v>
@@ -1171,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
         <v>48</v>
@@ -1180,7 +1180,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>16</v>
@@ -1201,7 +1201,7 @@
         <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
         <v>60</v>
@@ -1219,58 +1219,58 @@
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
         <v>32</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1398,10 +1398,10 @@
         <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
         <v>4.2</v>
@@ -1410,7 +1410,7 @@
         <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1473,7 +1473,7 @@
         <v>160</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>13</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1649,13 @@
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>4.9</v>
@@ -1664,7 +1664,7 @@
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.34</v>
@@ -1688,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>18.5</v>
@@ -1736,7 +1736,7 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1748,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
@@ -1760,25 +1760,25 @@
         <v>4.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
         <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="n">
         <v>2.82</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>1.75</v>
@@ -2145,7 +2145,7 @@
         <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -2178,7 +2178,7 @@
         <v>2.08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>18.5</v>
@@ -2214,7 +2214,7 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
         <v>150</v>
@@ -2235,37 +2235,37 @@
         <v>14.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AW7" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>4.2</v>
       </c>
       <c r="AY7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
       </c>
       <c r="BA7" t="n">
         <v>4.3</v>
@@ -2286,7 +2286,7 @@
         <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>3.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2384,22 +2384,22 @@
         <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
         <v>4.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -2408,10 +2408,10 @@
         <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
         <v>2.34</v>
@@ -2420,19 +2420,19 @@
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
         <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2489,10 +2489,10 @@
         <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>4.9</v>
@@ -2501,34 +2501,34 @@
         <v>5.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
         <v>4.9</v>
@@ -2537,7 +2537,7 @@
         <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG8" t="n">
         <v>5.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2641,28 +2641,28 @@
         <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="I9" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
         <v>1.78</v>
@@ -2674,7 +2674,7 @@
         <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
@@ -2683,10 +2683,10 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2713,7 +2713,7 @@
         <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>16</v>
@@ -2737,13 +2737,13 @@
         <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.199999999999999</v>
@@ -2752,10 +2752,10 @@
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.4</v>
@@ -2773,10 +2773,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
         <v>5.3</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2943,10 +2943,10 @@
         <v>1.75</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
         <v>32</v>
@@ -2958,19 +2958,19 @@
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
         <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -3006,7 +3006,7 @@
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -3018,7 +3018,7 @@
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -3039,16 +3039,16 @@
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
         <v>14.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="n">
         <v>3.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3424,10 +3424,10 @@
         <v>1.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q12" t="n">
         <v>1.42</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3905,61 +3905,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
         <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="O14" t="n">
         <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
         <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -3974,16 +3974,16 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>100</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
@@ -3995,10 +3995,10 @@
         <v>120</v>
       </c>
       <c r="AJ14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
         <v>65</v>
@@ -4007,100 +4007,100 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>160</v>
       </c>
       <c r="AP14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT14" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AU14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="AZ14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE14" t="n">
         <v>3.4</v>
       </c>
-      <c r="AY14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF14" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BN14" t="n">
         <v>4.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4159,70 +4159,70 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
         <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y15" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Z15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
         <v>10.5</v>
@@ -4240,91 +4240,91 @@
         <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
         <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AW15" t="n">
         <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
         <v>3.65</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
@@ -4336,16 +4336,16 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ15" t="n">
         <v>6.8</v>
@@ -4354,35 +4354,35 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>2.42</v>
       </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="G17" t="n">
         <v>10.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -4697,7 +4697,7 @@
         <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -4706,7 +4706,7 @@
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
         <v>2.08</v>
@@ -4715,7 +4715,7 @@
         <v>1.77</v>
       </c>
       <c r="V17" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
@@ -4730,7 +4730,7 @@
         <v>8.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB17" t="n">
         <v>27</v>
@@ -4772,67 +4772,67 @@
         <v>290</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ17" t="n">
         <v>12.5</v>
@@ -4844,43 +4844,43 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BN17" t="n">
         <v>12</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BT17" t="n">
         <v>3.9</v>
       </c>
       <c r="BU17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BV17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BX17" t="n">
         <v>30</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BZ17" t="n">
         <v>21</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
         <v>1.02</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="Q18" t="n">
         <v>1.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G20" t="n">
         <v>1.86</v>
@@ -5438,7 +5438,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>4.5</v>
@@ -5477,7 +5477,7 @@
         <v>2.82</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
         <v>2.16</v>
@@ -5507,7 +5507,7 @@
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -5537,16 +5537,16 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT20" t="n">
         <v>12.5</v>
@@ -5555,10 +5555,10 @@
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -5570,19 +5570,19 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
         <v>4.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G21" t="n">
         <v>1.88</v>
@@ -5692,16 +5692,16 @@
         <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K21" t="n">
         <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5713,10 +5713,10 @@
         <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R21" t="n">
         <v>1.43</v>
@@ -5725,7 +5725,7 @@
         <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U21" t="n">
         <v>2.14</v>
@@ -5737,7 +5737,7 @@
         <v>2.14</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
         <v>24</v>
@@ -5749,10 +5749,10 @@
         <v>130</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
         <v>24</v>
@@ -5761,13 +5761,13 @@
         <v>75</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>75</v>
@@ -5776,7 +5776,7 @@
         <v>24</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>40</v>
@@ -5791,16 +5791,16 @@
         <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AQ21" t="n">
         <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT21" t="n">
         <v>8.6</v>
@@ -5809,10 +5809,10 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -5821,28 +5821,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BF21" t="n">
         <v>7.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -5970,7 +5970,7 @@
         <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R22" t="n">
         <v>1.07</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
         <v>2.2</v>
@@ -6454,10 +6454,10 @@
         <v>3.4</v>
       </c>
       <c r="I24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J24" t="n">
         <v>3.85</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>4.5</v>
@@ -6496,7 +6496,7 @@
         <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X24" t="n">
         <v>34</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6953,37 +6953,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
         <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
         <v>1.92</v>
@@ -7001,10 +7001,10 @@
         <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
         <v>17.5</v>
@@ -7016,10 +7016,10 @@
         <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC26" t="n">
         <v>9.800000000000001</v>
@@ -7031,13 +7031,13 @@
         <v>50</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
@@ -7061,7 +7061,7 @@
         <v>48</v>
       </c>
       <c r="AP26" t="n">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
@@ -7070,7 +7070,7 @@
         <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT26" t="n">
         <v>8.6</v>
@@ -7082,7 +7082,7 @@
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX26" t="n">
         <v>12.5</v>
@@ -7094,25 +7094,25 @@
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BC26" t="n">
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF26" t="n">
         <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="n">
         <v>3.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7255,10 +7255,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O28" t="n">
         <v>1.16</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="S28" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -7748,13 +7748,13 @@
         <v>1.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="R29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="S29" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7766,7 +7766,7 @@
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>3.55</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I30" t="n">
         <v>2.32</v>
@@ -7999,10 +7999,10 @@
         <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R30" t="n">
         <v>1.41</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
         <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.37</v>
@@ -8382,7 +8382,7 @@
         <v>19</v>
       </c>
       <c r="BG31" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G32" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="H32" t="n">
         <v>4.9</v>
@@ -8489,10 +8489,10 @@
         <v>5.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.27</v>
@@ -8501,34 +8501,34 @@
         <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R32" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X32" t="n">
         <v>25</v>
@@ -8543,7 +8543,7 @@
         <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC32" t="n">
         <v>12</v>
@@ -8585,28 +8585,28 @@
         <v>75</v>
       </c>
       <c r="AP32" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AR32" t="n">
         <v>32</v>
       </c>
       <c r="AS32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT32" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV32" t="n">
         <v>17</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX32" t="n">
         <v>9.800000000000001</v>
@@ -8615,28 +8615,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC32" t="n">
         <v>12.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BE32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF32" t="n">
         <v>7.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH32" t="n">
         <v>4.1</v>
@@ -8666,7 +8666,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR32" t="n">
         <v>24</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>2.24</v>
       </c>
       <c r="J33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K33" t="n">
         <v>4.3</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
         <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q36" t="n">
         <v>1.18</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -9750,10 +9750,10 @@
         <v>1.31</v>
       </c>
       <c r="G37" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I37" t="n">
         <v>13</v>
@@ -9798,7 +9798,7 @@
         <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X37" t="n">
         <v>28</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10031,7 +10031,7 @@
         <v>1.01</v>
       </c>
       <c r="P38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q38" t="n">
         <v>1.02</v>
@@ -10040,7 +10040,7 @@
         <v>1.07</v>
       </c>
       <c r="S38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10533,7 +10533,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
         <v>1.17</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.74</v>
+        <v>5.3</v>
       </c>
       <c r="O41" t="n">
         <v>1.11</v>
@@ -10802,7 +10802,7 @@
         <v>1.61</v>
       </c>
       <c r="S41" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="T41" t="n">
         <v>1.4</v>
@@ -10874,7 +10874,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR41" t="n">
         <v>1.03</v>
@@ -10883,37 +10883,37 @@
         <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
         <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
         <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
         <v>1.03</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -11280,154 +11280,154 @@
         <v>3.6</v>
       </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J43" t="n">
         <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P43" t="n">
         <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S43" t="n">
         <v>2.56</v>
       </c>
       <c r="T43" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="U43" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="V43" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W43" t="n">
         <v>1.87</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS43" t="n">
         <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE43" t="n">
         <v>1.03</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG43" t="n">
         <v>1.01</v>
@@ -11442,13 +11442,13 @@
         <v>13</v>
       </c>
       <c r="BK43" t="n">
-        <v>5.6</v>
+        <v>2.34</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>21</v>
+        <v>2.86</v>
       </c>
       <c r="BN43" t="n">
         <v>7.4</v>
@@ -11460,13 +11460,13 @@
         <v>20</v>
       </c>
       <c r="BQ43" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="BR43" t="n">
         <v>34</v>
       </c>
       <c r="BS43" t="n">
-        <v>14</v>
+        <v>2.64</v>
       </c>
       <c r="BT43" t="n">
         <v>10.5</v>
@@ -11478,23 +11478,23 @@
         <v>40</v>
       </c>
       <c r="BW43" t="n">
-        <v>16</v>
+        <v>2.68</v>
       </c>
       <c r="BX43" t="n">
         <v>48</v>
       </c>
       <c r="BY43" t="n">
-        <v>19</v>
+        <v>2.7</v>
       </c>
       <c r="BZ43" t="n">
         <v>25</v>
       </c>
       <c r="CA43" t="n">
-        <v>10.5</v>
+        <v>2.56</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -11537,218 +11537,218 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
       </c>
       <c r="P44" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Q44" t="n">
         <v>1.02</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -11797,212 +11797,212 @@
         <v>1000</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S45" t="n">
         <v>1.05</v>
       </c>
-      <c r="O45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -12051,16 +12051,16 @@
         <v>4.3</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P46" t="n">
         <v>2.08</v>
@@ -12069,184 +12069,184 @@
         <v>1.74</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -863,7 +863,7 @@
         <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
         <v>5.2</v>
@@ -872,7 +872,7 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.41</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
         <v>2.66</v>
@@ -1129,7 +1129,7 @@
         <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
@@ -1165,22 +1165,22 @@
         <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Z3" t="n">
         <v>16.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB3" t="n">
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
         <v>16</v>
@@ -1216,7 +1216,7 @@
         <v>65</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>8.199999999999999</v>
@@ -1228,7 +1228,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1240,7 +1240,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1252,25 +1252,25 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
         <v>32</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1371,31 +1371,31 @@
         <v>1.87</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1404,16 +1404,16 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
         <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
         <v>2.14</v>
@@ -1479,10 +1479,10 @@
         <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1494,7 +1494,7 @@
         <v>18.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX4" t="n">
         <v>9</v>
@@ -1506,7 +1506,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB4" t="n">
         <v>17.5</v>
@@ -1515,16 +1515,16 @@
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF4" t="n">
         <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH4" t="n">
         <v>3.05</v>
@@ -1542,13 +1542,13 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN4" t="n">
         <v>4.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
         <v>13.5</v>
@@ -1575,7 +1575,7 @@
         <v>12</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
         <v>12.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
         <v>3.9</v>
@@ -1634,7 +1634,7 @@
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.47</v>
@@ -1643,31 +1643,31 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P5" t="n">
         <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
         <v>1.68</v>
@@ -1688,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
         <v>18.5</v>
@@ -1709,7 +1709,7 @@
         <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
         <v>38</v>
@@ -1736,10 +1736,10 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
@@ -1757,28 +1757,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="n">
         <v>2.82</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I6" t="n">
         <v>1.66</v>
@@ -1888,7 +1888,7 @@
         <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
@@ -1906,16 +1906,16 @@
         <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>2.04</v>
@@ -1927,7 +1927,7 @@
         <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
@@ -1987,7 +1987,7 @@
         <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>13</v>
@@ -1996,10 +1996,10 @@
         <v>20</v>
       </c>
       <c r="AU6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV6" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>8.6</v>
       </c>
       <c r="AW6" t="n">
         <v>13.5</v>
@@ -2020,7 +2020,7 @@
         <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
         <v>4.1</v>
@@ -2029,7 +2029,7 @@
         <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
         <v>6.6</v>
@@ -2044,16 +2044,16 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO6" t="n">
         <v>5.2</v>
@@ -2062,13 +2062,13 @@
         <v>55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>4.4</v>
@@ -2080,23 +2080,23 @@
         <v>10.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX6" t="n">
         <v>24</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>16.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
@@ -2154,13 +2154,13 @@
         <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -2181,7 +2181,7 @@
         <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
         <v>11</v>
@@ -2193,10 +2193,10 @@
         <v>24</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
@@ -2238,19 +2238,19 @@
         <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
         <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
@@ -2259,7 +2259,7 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
         <v>14</v>
@@ -2271,19 +2271,19 @@
         <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
         <v>8.800000000000001</v>
@@ -2292,13 +2292,13 @@
         <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2313,7 +2313,7 @@
         <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
         <v>9</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT7" t="n">
         <v>4.6</v>
@@ -2340,7 +2340,7 @@
         <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>23</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
         <v>5.1</v>
@@ -2408,22 +2408,22 @@
         <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
@@ -2441,7 +2441,7 @@
         <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
         <v>150</v>
@@ -2540,7 +2540,7 @@
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
         <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
@@ -2659,7 +2659,7 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.36</v>
@@ -2668,7 +2668,7 @@
         <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -2680,13 +2680,13 @@
         <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
         <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2704,7 +2704,7 @@
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
@@ -2719,7 +2719,7 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
         <v>50</v>
@@ -2734,7 +2734,7 @@
         <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
         <v>48</v>
@@ -2743,19 +2743,19 @@
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU9" t="n">
         <v>6.4</v>
@@ -2767,31 +2767,31 @@
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>2.96</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.12</v>
@@ -2922,25 +2922,25 @@
         <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3173,7 +3173,7 @@
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
         <v>1.42</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -3675,37 +3675,37 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.04</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
       </c>
       <c r="V13" t="n">
         <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -3717,10 +3717,10 @@
         <v>95</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>16.5</v>
@@ -3729,10 +3729,10 @@
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
         <v>23</v>
@@ -3768,7 +3768,7 @@
         <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
@@ -3780,10 +3780,10 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
         <v>9.6</v>
@@ -3792,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -3801,37 +3801,37 @@
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
         <v>3.8</v>
@@ -3840,13 +3840,13 @@
         <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR13" t="n">
         <v>34</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
         <v>7</v>
@@ -3858,23 +3858,23 @@
         <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>32</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4192,13 +4192,13 @@
         <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
         <v>1.85</v>
@@ -4228,7 +4228,7 @@
         <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
         <v>20</v>
@@ -4240,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
         <v>24</v>
@@ -4267,58 +4267,58 @@
         <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AQ15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT15" t="n">
         <v>3.4</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AU15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX15" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AY15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4951,13 +4951,13 @@
         <v>1.02</v>
       </c>
       <c r="P18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S18" t="n">
         <v>1.51</v>
@@ -4972,7 +4972,7 @@
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
         <v>4.5</v>
@@ -5444,7 +5444,7 @@
         <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -5453,28 +5453,28 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T20" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
         <v>1.28</v>
@@ -5483,112 +5483,112 @@
         <v>2.16</v>
       </c>
       <c r="X20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE20" t="n">
         <v>46</v>
       </c>
-      <c r="Y20" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>48</v>
-      </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK20" t="n">
         <v>17</v>
       </c>
-      <c r="AI20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AL20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="AT20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU20" t="n">
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.3</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BE20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BF20" t="n">
         <v>5.4</v>
       </c>
-      <c r="BF20" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG20" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH20" t="n">
         <v>5.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5695,13 +5695,13 @@
         <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
         <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,19 +6215,19 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
         <v>1.36</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S23" t="n">
         <v>1.38</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>3.25</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J24" t="n">
         <v>3.4</v>
@@ -6463,7 +6463,7 @@
         <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -6475,10 +6475,10 @@
         <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R24" t="n">
         <v>1.34</v>
@@ -6490,10 +6490,10 @@
         <v>1.74</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
         <v>1.74</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6747,11 +6747,11 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.02</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X25" t="n">
         <v>1000</v>
       </c>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7154,7 +7154,7 @@
         <v>6.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7231,34 +7231,34 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
         <v>1.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U27" t="n">
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
         <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="R28" t="n">
         <v>1.06</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="O29" t="n">
         <v>1.3</v>
@@ -7748,13 +7748,13 @@
         <v>1.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7766,7 +7766,7 @@
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>3.55</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I30" t="n">
         <v>2.34</v>
@@ -8140,7 +8140,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8170,7 +8170,7 @@
         <v>5.3</v>
       </c>
       <c r="BU30" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BV30" t="n">
         <v>16.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G35" t="n">
         <v>3.65</v>
@@ -9248,7 +9248,7 @@
         <v>2.08</v>
       </c>
       <c r="I35" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J35" t="n">
         <v>3.9</v>
@@ -9287,7 +9287,7 @@
         <v>2.46</v>
       </c>
       <c r="V35" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W35" t="n">
         <v>1.37</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="O42" t="n">
         <v>1.11</v>
@@ -11062,7 +11062,7 @@
         <v>1.18</v>
       </c>
       <c r="U42" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>1.94</v>
       </c>
       <c r="G43" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H43" t="n">
         <v>3.6</v>
@@ -11283,7 +11283,7 @@
         <v>4.2</v>
       </c>
       <c r="J43" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K43" t="n">
         <v>4.5</v>
@@ -11304,7 +11304,7 @@
         <v>2.36</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R43" t="n">
         <v>1.55</v>
@@ -11313,10 +11313,10 @@
         <v>2.46</v>
       </c>
       <c r="T43" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U43" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V43" t="n">
         <v>1.32</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>3.75</v>
       </c>
       <c r="G46" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H46" t="n">
         <v>1.91</v>
@@ -12054,13 +12054,13 @@
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P46" t="n">
         <v>2.08</v>
@@ -12069,34 +12069,34 @@
         <v>1.74</v>
       </c>
       <c r="R46" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S46" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T46" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="U46" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="V46" t="n">
         <v>1.87</v>
       </c>
       <c r="W46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z46" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB46" t="n">
         <v>22</v>
@@ -12105,13 +12105,13 @@
         <v>11.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF46" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG46" t="n">
         <v>21</v>
@@ -12120,79 +12120,79 @@
         <v>22</v>
       </c>
       <c r="AI46" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX46" t="n">
         <v>1.03</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
         <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -12544,13 +12544,13 @@
         <v>2.4</v>
       </c>
       <c r="G48" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H48" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="I48" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J48" t="n">
         <v>3.1</v>
@@ -12559,212 +12559,212 @@
         <v>3.55</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P48" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP48" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV48" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -12798,10 +12798,10 @@
         <v>1.89</v>
       </c>
       <c r="G49" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I49" t="n">
         <v>5.2</v>
@@ -12846,19 +12846,19 @@
         <v>1.24</v>
       </c>
       <c r="W49" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X49" t="n">
         <v>14.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA49" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB49" t="n">
         <v>9.199999999999999</v>
@@ -12867,7 +12867,7 @@
         <v>8.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE49" t="n">
         <v>80</v>
@@ -12882,7 +12882,7 @@
         <v>23</v>
       </c>
       <c r="AI49" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="n">
         <v>26</v>
@@ -12900,7 +12900,7 @@
         <v>18.5</v>
       </c>
       <c r="AO49" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP49" t="n">
         <v>10.5</v>
@@ -12909,10 +12909,10 @@
         <v>12</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT49" t="n">
         <v>6.8</v>
@@ -12924,7 +12924,7 @@
         <v>15</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX49" t="n">
         <v>9.6</v>
@@ -12933,10 +12933,10 @@
         <v>9</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB49" t="n">
         <v>19</v>
@@ -12945,16 +12945,16 @@
         <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF49" t="n">
         <v>12</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH49" t="n">
         <v>3.35</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <v>3.65</v>
       </c>
       <c r="L50" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
@@ -13085,10 +13085,10 @@
         <v>2.06</v>
       </c>
       <c r="R50" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S50" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T50" t="n">
         <v>1.83</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -13363,7 +13363,7 @@
         <v>12.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="n">
         <v>60</v>
@@ -13375,16 +13375,16 @@
         <v>7.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE51" t="n">
         <v>44</v>
       </c>
       <c r="AF51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG51" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH51" t="n">
         <v>23</v>
@@ -13420,7 +13420,7 @@
         <v>16</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT51" t="n">
         <v>8.800000000000001</v>
@@ -13432,7 +13432,7 @@
         <v>11.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX51" t="n">
         <v>16</v>
@@ -13444,25 +13444,25 @@
         <v>16.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="G52" t="n">
         <v>3.2</v>
@@ -13566,13 +13566,13 @@
         <v>2.68</v>
       </c>
       <c r="I52" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>2.7</v>
       </c>
       <c r="K52" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,22 +13581,22 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O52" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P52" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R52" t="n">
         <v>1.17</v>
       </c>
       <c r="S52" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13605,7 +13605,7 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W52" t="n">
         <v>1.45</v>
@@ -13728,49 +13728,49 @@
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -14173,58 +14173,58 @@
         <v>180</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -14319,220 +14319,220 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BJ55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ55" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -14576,31 +14576,31 @@
         <v>1.68</v>
       </c>
       <c r="G56" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H56" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="I56" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J56" t="n">
         <v>2.9</v>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P56" t="n">
         <v>1.76</v>
@@ -14609,184 +14609,184 @@
         <v>1.83</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ56" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -14830,13 +14830,13 @@
         <v>2.2</v>
       </c>
       <c r="G57" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H57" t="n">
         <v>3.35</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
         <v>2.78</v>
@@ -14845,202 +14845,202 @@
         <v>4.1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P57" t="n">
         <v>1.46</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ57" t="n">
         <v>0</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -15099,212 +15099,212 @@
         <v>4.1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P58" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="Q58" t="n">
         <v>1.79</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH58" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK58" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN58" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ58" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT58" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU58" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV58" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW58" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX58" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY58" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BZ58" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA58" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -15335,230 +15335,230 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P59" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AU59" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BH59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ59" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK59" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN59" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP59" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ59" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BR59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT59" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU59" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -15598,25 +15598,25 @@
         <v>2.76</v>
       </c>
       <c r="I60" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="K60" t="n">
         <v>3.45</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P60" t="n">
         <v>1.54</v>
@@ -15625,184 +15625,184 @@
         <v>2.22</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH60" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI60" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -15873,7 +15873,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q61" t="n">
         <v>2.18</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G62" t="n">
         <v>1.64</v>
       </c>
       <c r="H62" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="I62" t="n">
         <v>9.6</v>
@@ -16115,212 +16115,212 @@
         <v>4.7</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P62" t="n">
         <v>1.81</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>1.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -1153,7 +1153,7 @@
         <v>5.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
         <v>1.84</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
         <v>5.6</v>
@@ -1416,7 +1416,7 @@
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1485,7 +1485,7 @@
         <v>5.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.76</v>
@@ -2154,13 +2154,13 @@
         <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
         <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -2214,7 +2214,7 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
         <v>150</v>
@@ -2238,10 +2238,10 @@
         <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
         <v>14</v>
@@ -2253,7 +2253,7 @@
         <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -2262,10 +2262,10 @@
         <v>4.1</v>
       </c>
       <c r="AY7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
         <v>4.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
@@ -2432,7 +2432,7 @@
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
         <v>2.36</v>
@@ -2683,10 +2683,10 @@
         <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.12</v>
@@ -2913,52 +2913,52 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
         <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA10" t="n">
         <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>12.5</v>
@@ -2970,10 +2970,10 @@
         <v>27</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI10" t="n">
         <v>38</v>
@@ -2994,25 +2994,25 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -3024,31 +3024,31 @@
         <v>17.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
         <v>19</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3173,13 +3173,13 @@
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
         <v>1.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
         <v>1.42</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3424,13 +3424,13 @@
         <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.54</v>
+        <v>1.05</v>
       </c>
       <c r="R12" t="n">
         <v>1.07</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -3675,13 +3675,13 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
         <v>2.06</v>
@@ -3696,7 +3696,7 @@
         <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.35</v>
@@ -3708,7 +3708,7 @@
         <v>15.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
         <v>32</v>
@@ -3768,7 +3768,7 @@
         <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
@@ -3780,7 +3780,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3792,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -3801,16 +3801,16 @@
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
         <v>17.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH13" t="n">
         <v>3.25</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
@@ -3929,7 +3929,7 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O14" t="n">
         <v>1.45</v>
@@ -3956,7 +3956,7 @@
         <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="X14" t="n">
         <v>12</v>
@@ -4070,7 +4070,7 @@
         <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>4.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
         <v>3.7</v>
@@ -4216,7 +4216,7 @@
         <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
@@ -4225,25 +4225,25 @@
         <v>100</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
         <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
@@ -4261,64 +4261,64 @@
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AW15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY15" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>2.12</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
         <v>4.5</v>
@@ -5444,10 +5444,10 @@
         <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
@@ -5459,37 +5459,37 @@
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="S20" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X20" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -5498,16 +5498,16 @@
         <v>20</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -5516,10 +5516,10 @@
         <v>15.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AK20" t="n">
         <v>17</v>
@@ -5528,7 +5528,7 @@
         <v>24</v>
       </c>
       <c r="AM20" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
         <v>6.2</v>
@@ -5537,13 +5537,13 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AS20" t="n">
         <v>36</v>
@@ -5555,10 +5555,10 @@
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
         <v>14</v>
@@ -5570,7 +5570,7 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BB20" t="n">
         <v>15.5</v>
@@ -5582,16 +5582,16 @@
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI20" t="n">
         <v>4.1</v>
@@ -5600,59 +5600,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO20" t="n">
         <v>4.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
         <v>18.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BZ20" t="n">
         <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.35</v>
@@ -5707,34 +5707,34 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T21" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="U21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -5752,7 +5752,7 @@
         <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
         <v>24</v>
@@ -5791,28 +5791,28 @@
         <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU21" t="n">
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -5821,31 +5821,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC21" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BD21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE21" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC21" t="n">
+      <c r="BF21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH21" t="n">
         <v>3.85</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.9</v>
       </c>
       <c r="BI21" t="n">
         <v>3</v>
@@ -5854,13 +5854,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN21" t="n">
         <v>4.7</v>
@@ -5869,44 +5869,44 @@
         <v>3.55</v>
       </c>
       <c r="BP21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H22" t="n">
         <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J22" t="n">
         <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.23</v>
@@ -5961,25 +5961,25 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O22" t="n">
         <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q22" t="n">
         <v>1.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U22" t="n">
         <v>2.64</v>
@@ -5988,7 +5988,7 @@
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X22" t="n">
         <v>34</v>
@@ -6015,7 +6015,7 @@
         <v>40</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG22" t="n">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO22" t="n">
         <v>23</v>
@@ -6051,10 +6051,10 @@
         <v>16.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT22" t="n">
         <v>11.5</v>
@@ -6066,7 +6066,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX22" t="n">
         <v>12.5</v>
@@ -6078,7 +6078,7 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -6108,31 +6108,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO22" t="n">
         <v>4.4</v>
       </c>
       <c r="BP22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT22" t="n">
         <v>7.4</v>
@@ -6144,13 +6144,13 @@
         <v>23</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
         <v>27</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G24" t="n">
         <v>2.34</v>
@@ -6454,10 +6454,10 @@
         <v>3.25</v>
       </c>
       <c r="I24" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
         <v>3.8</v>
@@ -6469,31 +6469,31 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.74</v>
@@ -6529,7 +6529,7 @@
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>60</v>
@@ -6553,7 +6553,7 @@
         <v>48</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
@@ -6562,88 +6562,88 @@
         <v>17.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX24" t="n">
         <v>12.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC24" t="n">
         <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO24" t="n">
         <v>4</v>
       </c>
       <c r="BP24" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU24" t="n">
         <v>4.9</v>
@@ -6652,23 +6652,23 @@
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         <v>2.56</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.31</v>
@@ -6977,19 +6977,19 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
         <v>3.15</v>
@@ -6998,7 +6998,7 @@
         <v>1.7</v>
       </c>
       <c r="U26" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V26" t="n">
         <v>1.46</v>
@@ -7007,58 +7007,58 @@
         <v>1.64</v>
       </c>
       <c r="X26" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA26" t="n">
         <v>65</v>
       </c>
       <c r="AB26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH26" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AI26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
         <v>21</v>
       </c>
-      <c r="AG26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK26" t="n">
+      <c r="AO26" t="n">
         <v>32</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>34</v>
       </c>
       <c r="AP26" t="n">
         <v>14</v>
@@ -7067,52 +7067,52 @@
         <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.1</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="AX26" t="n">
         <v>14.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BF26" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH26" t="n">
         <v>3.6</v>
@@ -7124,7 +7124,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7136,7 +7136,7 @@
         <v>5.5</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
@@ -7154,7 +7154,7 @@
         <v>6.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7246,7 +7246,7 @@
         <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T27" t="n">
         <v>1.03</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>3.35</v>
       </c>
       <c r="G30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H30" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I30" t="n">
         <v>2.34</v>
@@ -7987,7 +7987,7 @@
         <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -8014,7 +8014,7 @@
         <v>1.72</v>
       </c>
       <c r="U30" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V30" t="n">
         <v>1.74</v>
@@ -8113,19 +8113,19 @@
         <v>26</v>
       </c>
       <c r="BB30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC30" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC30" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF30" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>5.1</v>
       </c>
       <c r="BG30" t="n">
         <v>14.5</v>
@@ -8179,7 +8179,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY30" t="n">
         <v>10</v>
@@ -8188,11 +8188,11 @@
         <v>24</v>
       </c>
       <c r="CA30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -8229,10 +8229,10 @@
         <v>3.1</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I31" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -8340,7 +8340,7 @@
         <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -8364,19 +8364,19 @@
         <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB31" t="n">
         <v>36</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF31" t="n">
         <v>19</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I32" t="n">
         <v>1.54</v>
@@ -8510,10 +8510,10 @@
         <v>3.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="R32" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="S32" t="n">
         <v>1.98</v>
@@ -8528,7 +8528,7 @@
         <v>2.84</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
         <v>44</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -9520,16 +9520,16 @@
         <v>5.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
         <v>1.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S36" t="n">
         <v>2.52</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O37" t="n">
         <v>1.18</v>
@@ -9783,7 +9783,7 @@
         <v>1.18</v>
       </c>
       <c r="R37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="S37" t="n">
         <v>1.18</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -10509,20 +10509,20 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="n">
         <v>1.04</v>
       </c>
-      <c r="G40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1.03</v>
-      </c>
       <c r="K40" t="n">
         <v>1000</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
         <v>1.17</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>1.94</v>
       </c>
       <c r="G43" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H43" t="n">
         <v>3.6</v>
@@ -11292,7 +11292,7 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N43" t="n">
         <v>5</v>
@@ -11322,7 +11322,7 @@
         <v>1.32</v>
       </c>
       <c r="W43" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X43" t="n">
         <v>28</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
         <v>2.18</v>
       </c>
       <c r="V46" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W46" t="n">
         <v>1.29</v>
@@ -12159,7 +12159,7 @@
         <v>6.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW46" t="n">
         <v>14.5</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -12544,10 +12544,10 @@
         <v>2.4</v>
       </c>
       <c r="G48" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H48" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="I48" t="n">
         <v>3.65</v>
@@ -12559,22 +12559,22 @@
         <v>3.55</v>
       </c>
       <c r="L48" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O48" t="n">
         <v>1.43</v>
       </c>
       <c r="P48" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R48" t="n">
         <v>1.19</v>
@@ -12592,10 +12592,10 @@
         <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X48" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y48" t="n">
         <v>14.5</v>
@@ -12652,37 +12652,37 @@
         <v>2.42</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AR48" t="n">
         <v>16.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AX48" t="n">
         <v>10</v>
       </c>
       <c r="AY48" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BB48" t="n">
         <v>24</v>
@@ -12691,34 +12691,34 @@
         <v>21</v>
       </c>
       <c r="BD48" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BF48" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BG48" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BJ48" t="n">
         <v>14.5</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BN48" t="n">
         <v>7</v>
@@ -12730,13 +12730,13 @@
         <v>29</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BR48" t="n">
         <v>50</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BT48" t="n">
         <v>8.6</v>
@@ -12748,23 +12748,23 @@
         <v>40</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BZ48" t="n">
         <v>50</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -13067,22 +13067,22 @@
         <v>3.65</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P50" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R50" t="n">
         <v>1.26</v>
@@ -13091,124 +13091,124 @@
         <v>4.2</v>
       </c>
       <c r="T50" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U50" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="V50" t="n">
         <v>1.25</v>
       </c>
       <c r="W50" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X50" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y50" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV50" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z50" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC50" t="n">
+      <c r="AW50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY50" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD50" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AQ50" t="n">
+      <c r="AZ50" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD50" t="n">
         <v>10</v>
       </c>
-      <c r="AR50" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BE50" t="n">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="BF50" t="n">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="BG50" t="n">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
         <v>2.64</v>
       </c>
       <c r="O52" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P52" t="n">
         <v>1.61</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -13811,19 +13811,19 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G53" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H53" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I53" t="n">
         <v>1.91</v>
       </c>
       <c r="J53" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K53" t="n">
         <v>4.5</v>
@@ -13835,16 +13835,16 @@
         <v>1.05</v>
       </c>
       <c r="N53" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O53" t="n">
         <v>1.26</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="R53" t="n">
         <v>1.39</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
         <v>1.45</v>
       </c>
       <c r="M55" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N55" t="n">
         <v>2.68</v>
@@ -14427,64 +14427,64 @@
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BH55" t="n">
         <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
         <v>2.9</v>
       </c>
       <c r="K56" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14606,7 +14606,7 @@
         <v>1.76</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R56" t="n">
         <v>1.25</v>
@@ -14744,49 +14744,49 @@
         <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN56" t="n">
         <v>1000</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT56" t="n">
         <v>1000</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ56" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>2.2</v>
       </c>
       <c r="G57" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H57" t="n">
         <v>3.35</v>
@@ -14863,10 +14863,10 @@
         <v>2.44</v>
       </c>
       <c r="R57" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S57" t="n">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -14878,7 +14878,7 @@
         <v>1.28</v>
       </c>
       <c r="W57" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -15081,112 +15081,112 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G58" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="H58" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I58" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K58" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L58" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M58" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N58" t="n">
         <v>3.8</v>
       </c>
       <c r="O58" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P58" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R58" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S58" t="n">
         <v>2.72</v>
       </c>
       <c r="T58" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U58" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V58" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W58" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="X58" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z58" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA58" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB58" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD58" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF58" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH58" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI58" t="n">
         <v>60</v>
       </c>
       <c r="AJ58" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AK58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL58" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM58" t="n">
         <v>90</v>
       </c>
       <c r="AN58" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AO58" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP58" t="n">
         <v>1.03</v>
@@ -15237,19 +15237,19 @@
         <v>1.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG58" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH58" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI58" t="n">
         <v>3</v>
       </c>
       <c r="BJ58" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK58" t="n">
         <v>7.2</v>
@@ -15261,50 +15261,50 @@
         <v>1.01</v>
       </c>
       <c r="BN58" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO58" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BQ58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BR58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BT58" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BU58" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BV58" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW58" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ58" t="n">
         <v>21</v>
       </c>
-      <c r="BX58" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY58" t="n">
-        <v>28</v>
-      </c>
-      <c r="BZ58" t="n">
-        <v>23</v>
-      </c>
       <c r="CA58" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -15335,22 +15335,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="G59" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="H59" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="J59" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="K59" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L59" t="n">
         <v>1.54</v>
@@ -15359,19 +15359,19 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="O59" t="n">
         <v>1.5</v>
       </c>
       <c r="P59" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="R59" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S59" t="n">
         <v>4.7</v>
@@ -15380,19 +15380,19 @@
         <v>1.01</v>
       </c>
       <c r="U59" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V59" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="W59" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
       </c>
       <c r="Y59" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z59" t="n">
         <v>1000</v>
@@ -15404,22 +15404,22 @@
         <v>1000</v>
       </c>
       <c r="AC59" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD59" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE59" t="n">
         <v>1000</v>
       </c>
       <c r="AF59" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG59" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI59" t="n">
         <v>1000</v>
@@ -15443,94 +15443,94 @@
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AU59" t="n">
-        <v>6.4</v>
+        <v>1.39</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="BH59" t="n">
         <v>1000</v>
       </c>
       <c r="BI59" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BJ59" t="n">
         <v>15.5</v>
       </c>
       <c r="BK59" t="n">
-        <v>7.2</v>
+        <v>1.57</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>22</v>
+        <v>1.75</v>
       </c>
       <c r="BN59" t="n">
         <v>6.4</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP59" t="n">
         <v>26</v>
       </c>
       <c r="BQ59" t="n">
-        <v>12</v>
+        <v>1.64</v>
       </c>
       <c r="BR59" t="n">
         <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>22</v>
+        <v>1.7</v>
       </c>
       <c r="BT59" t="n">
         <v>9.6</v>
@@ -15542,23 +15542,23 @@
         <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>22</v>
+        <v>1.7</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>22</v>
+        <v>1.71</v>
       </c>
       <c r="BZ59" t="n">
         <v>1000</v>
       </c>
       <c r="CA59" t="n">
-        <v>22</v>
+        <v>1.7</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -15589,22 +15589,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G60" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H60" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J60" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K60" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15616,31 +15616,31 @@
         <v>2.84</v>
       </c>
       <c r="O60" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P60" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W60" t="n">
         <v>1.54</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.57</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -15760,49 +15760,49 @@
         <v>1000</v>
       </c>
       <c r="BK60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL60" t="n">
         <v>1000</v>
       </c>
       <c r="BM60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN60" t="n">
         <v>1000</v>
       </c>
       <c r="BO60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP60" t="n">
         <v>1000</v>
       </c>
       <c r="BQ60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR60" t="n">
         <v>1000</v>
       </c>
       <c r="BS60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT60" t="n">
         <v>1000</v>
       </c>
       <c r="BU60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV60" t="n">
         <v>1000</v>
       </c>
       <c r="BW60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX60" t="n">
         <v>1000</v>
       </c>
       <c r="BY60" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
         <v>1.96</v>
       </c>
       <c r="G61" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="H61" t="n">
         <v>3.2</v>
@@ -15861,202 +15861,202 @@
         <v>5.7</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P61" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="Q61" t="n">
         <v>2.18</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI61" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BJ61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BL61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BN61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BP61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BR61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BT61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BV61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BX61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BZ61" t="n">
         <v>0</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
         <v>9.6</v>
       </c>
       <c r="J62" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K62" t="n">
         <v>4.7</v>
@@ -16118,13 +16118,13 @@
         <v>1.01</v>
       </c>
       <c r="M62" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N62" t="n">
         <v>3.1</v>
       </c>
       <c r="O62" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P62" t="n">
         <v>1.81</v>
@@ -16145,118 +16145,118 @@
         <v>1.75</v>
       </c>
       <c r="V62" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W62" t="n">
         <v>2.56</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y62" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z62" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA62" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB62" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD62" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE62" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF62" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG62" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI62" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK62" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL62" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM62" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN62" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO62" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB62"/>
+  <dimension ref="A1:CB63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -1141,7 +1141,7 @@
         <v>1.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -1156,7 +1156,7 @@
         <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
         <v>1.55</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
         <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
@@ -1640,10 +1640,10 @@
         <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
         <v>1.49</v>
@@ -1652,7 +1652,7 @@
         <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1661,10 +1661,10 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
@@ -1673,58 +1673,58 @@
         <v>1.68</v>
       </c>
       <c r="X5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y5" t="n">
         <v>11</v>
       </c>
-      <c r="Y5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>310</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>8.4</v>
@@ -1736,7 +1736,7 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1745,70 +1745,70 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.8</v>
+        <v>28</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO5" t="n">
         <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,32 +1817,32 @@
         <v>11.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
         <v>5.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>12</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
         <v>1.76</v>
@@ -2160,7 +2160,7 @@
         <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -2244,7 +2244,7 @@
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
         <v>12.5</v>
@@ -2253,7 +2253,7 @@
         <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -2292,7 +2292,7 @@
         <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>4.5</v>
@@ -2396,7 +2396,7 @@
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.49</v>
@@ -2414,16 +2414,16 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
@@ -2432,7 +2432,7 @@
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
@@ -2683,7 +2683,7 @@
         <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
         <v>1.43</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3143,46 +3143,46 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.09</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
         <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
@@ -3666,7 +3666,7 @@
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -3684,7 +3684,7 @@
         <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
         <v>1.31</v>
@@ -3693,10 +3693,10 @@
         <v>3.85</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
         <v>1.35</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
         <v>3.7</v>
@@ -4070,7 +4070,7 @@
         <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
         <v>2.62</v>
@@ -4437,7 +4437,7 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
@@ -4461,10 +4461,10 @@
         <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
@@ -4488,7 +4488,7 @@
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF16" t="n">
         <v>970</v>
@@ -4515,64 +4515,64 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
         <v>46</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY16" t="n">
         <v>3.95</v>
       </c>
-      <c r="AY16" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
         <v>1.91</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
         <v>1.46</v>
@@ -5486,7 +5486,7 @@
         <v>85</v>
       </c>
       <c r="Y20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z20" t="n">
         <v>100</v>
@@ -5498,31 +5498,31 @@
         <v>20</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
         <v>30</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL20" t="n">
         <v>24</v>
@@ -5558,7 +5558,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
         <v>14</v>
@@ -5573,13 +5573,13 @@
         <v>22</v>
       </c>
       <c r="BB20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE20" t="n">
         <v>29</v>
@@ -5588,7 +5588,7 @@
         <v>5.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BH20" t="n">
         <v>5.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
@@ -5791,16 +5791,16 @@
         <v>75</v>
       </c>
       <c r="AP21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>4</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT21" t="n">
         <v>8.800000000000001</v>
@@ -5809,10 +5809,10 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -5821,28 +5821,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB21" t="n">
         <v>4</v>
       </c>
-      <c r="BA21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF21" t="n">
         <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.85</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.32</v>
@@ -6484,7 +6484,7 @@
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
         <v>1.75</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>2.56</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I26" t="n">
         <v>3.2</v>
@@ -6977,7 +6977,7 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
@@ -7103,7 +7103,7 @@
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE26" t="n">
         <v>32</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7246,7 +7246,7 @@
         <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T27" t="n">
         <v>1.03</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.29</v>
@@ -8017,7 +8017,7 @@
         <v>2.28</v>
       </c>
       <c r="V30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W30" t="n">
         <v>1.4</v>
@@ -8038,22 +8038,22 @@
         <v>17.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
         <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG30" t="n">
         <v>17.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>44</v>
@@ -8113,19 +8113,19 @@
         <v>26</v>
       </c>
       <c r="BB30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF30" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>5.2</v>
       </c>
       <c r="BG30" t="n">
         <v>14.5</v>
@@ -8140,7 +8140,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK30" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8152,7 +8152,7 @@
         <v>6.6</v>
       </c>
       <c r="BO30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP30" t="n">
         <v>26</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G31" t="n">
         <v>3.1</v>
@@ -8232,13 +8232,13 @@
         <v>2.52</v>
       </c>
       <c r="I31" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.37</v>
@@ -8250,7 +8250,7 @@
         <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P31" t="n">
         <v>2.02</v>
@@ -8262,7 +8262,7 @@
         <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
         <v>1.7</v>
@@ -8298,7 +8298,7 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF31" t="n">
         <v>23</v>
@@ -8310,7 +8310,7 @@
         <v>17.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ31" t="n">
         <v>60</v>
@@ -8325,7 +8325,7 @@
         <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO31" t="n">
         <v>23</v>
@@ -8340,7 +8340,7 @@
         <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -8364,19 +8364,19 @@
         <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB31" t="n">
         <v>36</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF31" t="n">
         <v>19</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -8495,19 +8495,19 @@
         <v>5.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.11</v>
       </c>
       <c r="P32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q32" t="n">
         <v>1.39</v>
@@ -8522,7 +8522,7 @@
         <v>1.58</v>
       </c>
       <c r="U32" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V32" t="n">
         <v>2.84</v>
@@ -8642,10 +8642,10 @@
         <v>5.4</v>
       </c>
       <c r="BI32" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BJ32" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
         <v>5.7</v>
@@ -8654,7 +8654,7 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="BN32" t="n">
         <v>11</v>
@@ -8666,13 +8666,13 @@
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="BT32" t="n">
         <v>4.7</v>
@@ -8684,13 +8684,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BW32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H34" t="n">
         <v>4.9</v>
@@ -9000,7 +9000,7 @@
         <v>4.1</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L34" t="n">
         <v>1.27</v>
@@ -9015,28 +9015,28 @@
         <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
         <v>2.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U34" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V34" t="n">
         <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X34" t="n">
         <v>24</v>
@@ -9054,7 +9054,7 @@
         <v>12.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD34" t="n">
         <v>24</v>
@@ -9066,7 +9066,7 @@
         <v>14</v>
       </c>
       <c r="AG34" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH34" t="n">
         <v>22</v>
@@ -9102,58 +9102,58 @@
         <v>32</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU34" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>8.4</v>
       </c>
       <c r="AV34" t="n">
         <v>17</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC34" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH34" t="n">
         <v>4.1</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK34" t="n">
         <v>5</v>
@@ -9162,7 +9162,7 @@
         <v>110</v>
       </c>
       <c r="BM34" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN34" t="n">
         <v>4.8</v>
@@ -9198,7 +9198,7 @@
         <v>44</v>
       </c>
       <c r="BY34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ34" t="n">
         <v>18</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -9245,16 +9245,16 @@
         <v>3.65</v>
       </c>
       <c r="H35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I35" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J35" t="n">
         <v>3.9</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.25</v>
@@ -9263,7 +9263,7 @@
         <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>1.21</v>
@@ -9272,25 +9272,25 @@
         <v>2.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R35" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S35" t="n">
         <v>2.58</v>
       </c>
       <c r="T35" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U35" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V35" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W35" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X35" t="n">
         <v>27</v>
@@ -9347,19 +9347,19 @@
         <v>13.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>11.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS35" t="n">
         <v>19</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AU35" t="n">
         <v>8.4</v>
@@ -9368,16 +9368,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AX35" t="n">
         <v>20</v>
       </c>
       <c r="AY35" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA35" t="n">
         <v>20</v>
@@ -9386,10 +9386,10 @@
         <v>4.1</v>
       </c>
       <c r="BC35" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE35" t="n">
         <v>4.1</v>
@@ -9398,7 +9398,7 @@
         <v>19</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH35" t="n">
         <v>4.2</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G36" t="n">
         <v>1.36</v>
@@ -9505,7 +9505,7 @@
         <v>13</v>
       </c>
       <c r="J36" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K36" t="n">
         <v>6.4</v>
@@ -9529,22 +9529,22 @@
         <v>1.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S36" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V36" t="n">
         <v>1.08</v>
       </c>
       <c r="W36" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X36" t="n">
         <v>28</v>
@@ -9571,7 +9571,7 @@
         <v>210</v>
       </c>
       <c r="AF36" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -9583,7 +9583,7 @@
         <v>160</v>
       </c>
       <c r="AJ36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK36" t="n">
         <v>14.5</v>
@@ -9595,7 +9595,7 @@
         <v>190</v>
       </c>
       <c r="AN36" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AO36" t="n">
         <v>290</v>
@@ -9607,52 +9607,52 @@
         <v>28</v>
       </c>
       <c r="AR36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV36" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AW36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BA36" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB36" t="n">
         <v>9.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH36" t="n">
         <v>4.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I37" t="n">
         <v>1000</v>
@@ -9771,7 +9771,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O37" t="n">
         <v>1.18</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -10001,13 +10001,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G38" t="n">
         <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -10515,13 +10515,13 @@
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="O42" t="n">
         <v>1.11</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
         <v>5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
         <v>6.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
         <v>14.5</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -12335,10 +12335,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G48" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H48" t="n">
         <v>3.15</v>
@@ -12562,10 +12562,10 @@
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N48" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O48" t="n">
         <v>1.43</v>
@@ -12583,16 +12583,16 @@
         <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U48" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V48" t="n">
         <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X48" t="n">
         <v>13</v>
@@ -12685,10 +12685,10 @@
         <v>2.88</v>
       </c>
       <c r="BB48" t="n">
-        <v>24</v>
+        <v>2.82</v>
       </c>
       <c r="BC48" t="n">
-        <v>21</v>
+        <v>2.8</v>
       </c>
       <c r="BD48" t="n">
         <v>2.86</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
         <v>3.5</v>
       </c>
       <c r="K49" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L49" t="n">
         <v>1.38</v>
@@ -12825,7 +12825,7 @@
         <v>1.37</v>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
         <v>2.1</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -13040,239 +13040,239 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.95</v>
+        <v>2.74</v>
       </c>
       <c r="G50" t="n">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="H50" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L50" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M50" t="n">
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O50" t="n">
         <v>1.41</v>
       </c>
       <c r="P50" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R50" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T50" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="U50" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB50" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AC50" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD50" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF50" t="n">
         <v>19</v>
       </c>
-      <c r="AE50" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AG50" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI50" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ50" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AK50" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AL50" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AM50" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN50" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="AO50" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AP50" t="n">
         <v>10</v>
       </c>
       <c r="AQ50" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AS50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV50" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT50" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>16.5</v>
       </c>
-      <c r="AW50" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX50" t="n">
+      <c r="BA50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ50" t="n">
         <v>10</v>
       </c>
-      <c r="AY50" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI50" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ50" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BK50" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BN50" t="n">
         <v>5.8</v>
       </c>
       <c r="BO50" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BU50" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV50" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -13294,31 +13294,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="H51" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K51" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -13327,206 +13327,206 @@
         <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
         <v>1.41</v>
       </c>
       <c r="P51" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R51" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S51" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T51" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V51" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="W51" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="X51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y51" t="n">
         <v>14</v>
       </c>
-      <c r="Y51" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Z51" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD51" t="n">
         <v>19</v>
       </c>
-      <c r="AA51" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AE51" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AF51" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AG51" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH51" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI51" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ51" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AK51" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AL51" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM51" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN51" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AO51" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AP51" t="n">
         <v>10</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AR51" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AS51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU51" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU51" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ51" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
         <v>1.17</v>
       </c>
       <c r="S52" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
         <v>3.25</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
         <v>1.14</v>
@@ -14227,13 +14227,13 @@
         <v>4.5</v>
       </c>
       <c r="BH54" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ54" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK54" t="n">
         <v>1.01</v>
@@ -14245,13 +14245,13 @@
         <v>1.01</v>
       </c>
       <c r="BN54" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO54" t="n">
         <v>1.01</v>
       </c>
       <c r="BP54" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ54" t="n">
         <v>1.01</v>
@@ -14263,13 +14263,13 @@
         <v>1.01</v>
       </c>
       <c r="BT54" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU54" t="n">
         <v>1.01</v>
       </c>
       <c r="BV54" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
         <v>1.59</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R55" t="n">
         <v>1.21</v>
@@ -14484,7 +14484,7 @@
         <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -14573,157 +14573,157 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J56" t="n">
         <v>3.5</v>
       </c>
-      <c r="I56" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.9</v>
-      </c>
       <c r="K56" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O56" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P56" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R56" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S56" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T56" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U56" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V56" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W56" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF56" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW56" t="n">
         <v>1.03</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE56" t="n">
         <v>1.03</v>
@@ -14732,7 +14732,7 @@
         <v>1.01</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH56" t="n">
         <v>4.2</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15114,7 @@
         <v>2.06</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R58" t="n">
         <v>1.42</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -15335,166 +15335,166 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.09</v>
+        <v>2.18</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="H59" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I59" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="K59" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L59" t="n">
         <v>1.54</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N59" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
         <v>1.5</v>
       </c>
       <c r="P59" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S59" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U59" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V59" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="W59" t="n">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="X59" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y59" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG59" t="n">
         <v>14</v>
       </c>
-      <c r="Z59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AH59" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI59" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK59" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL59" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM59" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN59" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO59" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.39</v>
+        <v>6.8</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.39</v>
+        <v>20</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.39</v>
+        <v>6.4</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.39</v>
+        <v>6.4</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.31</v>
+        <v>12.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.27</v>
+        <v>9.4</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.26</v>
+        <v>8.6</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.32</v>
+        <v>16.5</v>
       </c>
       <c r="BA59" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.39</v>
+        <v>3.95</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.39</v>
+        <v>3.95</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.39</v>
+        <v>21</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="BH59" t="n">
         <v>1000</v>
@@ -15518,7 +15518,7 @@
         <v>6.4</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP59" t="n">
         <v>26</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -15592,16 +15592,16 @@
         <v>2.44</v>
       </c>
       <c r="G60" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="H60" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I60" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="K60" t="n">
         <v>3.5</v>
@@ -15619,7 +15619,7 @@
         <v>1.39</v>
       </c>
       <c r="P60" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="Q60" t="n">
         <v>2.12</v>
@@ -15637,10 +15637,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W60" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -15834,239 +15834,239 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="G61" t="n">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="H61" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W61" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X61" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT61" t="n">
         <v>3.2</v>
       </c>
-      <c r="I61" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K61" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC61" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH61" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ61" t="n">
         <v>1000</v>
       </c>
       <c r="BK61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BN61" t="n">
         <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BP61" t="n">
         <v>1000</v>
       </c>
       <c r="BQ61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BR61" t="n">
         <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BT61" t="n">
         <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BV61" t="n">
         <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BX61" t="n">
         <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="BZ61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -16088,239 +16088,493 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="G62" t="n">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="H62" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="I62" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="K62" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
       </c>
       <c r="M62" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="O62" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="P62" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="R62" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="S62" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="T62" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U62" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V62" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="W62" t="n">
-        <v>2.56</v>
+        <v>1.59</v>
       </c>
       <c r="X62" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y62" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z62" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA62" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC62" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD62" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE62" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG62" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH62" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI62" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ62" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK62" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL62" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM62" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN62" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO62" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AQ62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY62" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB62" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H63" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K63" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR62" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB62" t="inlineStr">
-        <is>
-          <t>2026-07-02 22:42:30</t>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB63" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB64"/>
+  <dimension ref="A1:CB65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
@@ -899,127 +899,127 @@
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
         <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.49</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.56</v>
+        <v>3.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.56</v>
+        <v>3.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.56</v>
+        <v>3.75</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.56</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.56</v>
+        <v>3.45</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.56</v>
+        <v>3.35</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.56</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.49</v>
+        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.48</v>
+        <v>3.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.56</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.56</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI2" t="n">
         <v>2.48</v>
@@ -1028,59 +1028,59 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>2.02</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="BN2" t="n">
-        <v>24</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -1141,16 +1141,16 @@
         <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
@@ -1159,10 +1159,10 @@
         <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>9.199999999999999</v>
@@ -1180,40 +1180,40 @@
         <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
         <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
         <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
@@ -1228,10 +1228,10 @@
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1240,37 +1240,37 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="n">
         <v>2.82</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>1.77</v>
       </c>
       <c r="G4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H4" t="n">
         <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1395,7 +1395,7 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.22</v>
@@ -1404,7 +1404,7 @@
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
         <v>2.08</v>
@@ -1416,7 +1416,7 @@
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
         <v>12</v>
@@ -1470,7 +1470,7 @@
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP4" t="n">
         <v>10.5</v>
@@ -1533,62 +1533,62 @@
         <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>55</v>
       </c>
       <c r="BW4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA4" t="n">
         <v>12</v>
       </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>10</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
@@ -1640,19 +1640,19 @@
         <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1661,16 +1661,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
         <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X5" t="n">
         <v>9.6</v>
@@ -1694,7 +1694,7 @@
         <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="AF5" t="n">
         <v>13.5</v>
@@ -1712,10 +1712,10 @@
         <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1727,16 +1727,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AT5" t="n">
         <v>7.4</v>
@@ -1745,10 +1745,10 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1757,25 +1757,25 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB5" t="n">
         <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG5" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>10.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>12</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>1.57</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
@@ -1921,7 +1921,7 @@
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1951,7 +1951,7 @@
         <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
         <v>24</v>
@@ -2002,7 +2002,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
         <v>7.4</v>
@@ -2017,19 +2017,19 @@
         <v>19</v>
       </c>
       <c r="BB6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
         <v>6.8</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2074,13 +2074,13 @@
         <v>4.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
         <v>10.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>24</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -2145,13 +2145,13 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
@@ -2175,16 +2175,16 @@
         <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>14</v>
@@ -2259,7 +2259,7 @@
         <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
         <v>13.5</v>
@@ -2268,22 +2268,22 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
         <v>9.4</v>
@@ -2292,7 +2292,7 @@
         <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
         <v>2.1</v>
@@ -2390,13 +2390,13 @@
         <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.49</v>
@@ -2408,31 +2408,31 @@
         <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2489,10 +2489,10 @@
         <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>5</v>
@@ -2507,19 +2507,19 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
         <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>5</v>
@@ -2537,7 +2537,7 @@
         <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BG8" t="n">
         <v>5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2641,19 +2641,19 @@
         <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2671,7 +2671,7 @@
         <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>3.8</v>
@@ -2680,37 +2680,37 @@
         <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB9" t="n">
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="n">
         <v>25</v>
@@ -2719,40 +2719,40 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
         <v>48</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
         <v>48</v>
       </c>
       <c r="AO9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2761,7 +2761,7 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
@@ -2776,22 +2776,22 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG9" t="n">
         <v>19</v>
@@ -2800,13 +2800,13 @@
         <v>3.25</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="BJ9" t="n">
         <v>10</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,37 +2818,37 @@
         <v>6.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU9" t="n">
         <v>4.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J10" t="n">
         <v>3.65</v>
@@ -2925,16 +2925,16 @@
         <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
         <v>1.67</v>
@@ -2946,7 +2946,7 @@
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
         <v>18</v>
@@ -2961,10 +2961,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
         <v>27</v>
@@ -3042,7 +3042,7 @@
         <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
         <v>19</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3164,7 +3164,7 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>1.08</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
         <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -3687,22 +3687,22 @@
         <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
         <v>3.85</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
         <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X13" t="n">
         <v>15.5</v>
@@ -3750,13 +3750,13 @@
         <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -3765,10 +3765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
@@ -3780,10 +3780,10 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
         <v>9.6</v>
@@ -3795,13 +3795,13 @@
         <v>5.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
         <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
         <v>5.7</v>
@@ -3810,25 +3810,25 @@
         <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ13" t="n">
         <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
@@ -3837,44 +3837,44 @@
         <v>3.8</v>
       </c>
       <c r="BP13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR13" t="n">
         <v>32</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ13" t="n">
         <v>30</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3905,70 +3905,70 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3977,22 +3977,22 @@
         <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF14" t="n">
         <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ14" t="n">
         <v>32</v>
@@ -4001,7 +4001,7 @@
         <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -4010,67 +4010,67 @@
         <v>28</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.22</v>
+        <v>4.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.87</v>
+        <v>3.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.92</v>
+        <v>3.75</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.26</v>
+        <v>5.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.28</v>
+        <v>3.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="BH14" t="n">
         <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4082,13 +4082,13 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4100,35 +4100,35 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
         <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
         <v>13.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
         <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK15" t="n">
         <v>36</v>
       </c>
-      <c r="AK15" t="n">
-        <v>32</v>
-      </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY15" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AZ15" t="n">
         <v>6</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BA15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7</v>
       </c>
-      <c r="AT15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="BE15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN15" t="n">
         <v>5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA15" t="n">
+      <c r="BO15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="n">
         <v>2.86</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -4437,22 +4437,22 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.79</v>
@@ -4461,7 +4461,7 @@
         <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
         <v>1.58</v>
@@ -4524,55 +4524,55 @@
         <v>3.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AR16" t="n">
         <v>3.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AV16" t="n">
         <v>3.7</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ16" t="n">
         <v>3.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BE16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG16" t="n">
         <v>3.7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3.5</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>1.96</v>
@@ -4706,13 +4706,13 @@
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
         <v>2.78</v>
@@ -4724,7 +4724,7 @@
         <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z17" t="n">
         <v>9.6</v>
@@ -4751,10 +4751,10 @@
         <v>38</v>
       </c>
       <c r="AH17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>410</v>
@@ -4775,55 +4775,55 @@
         <v>10.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AQ17" t="n">
         <v>3.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="AS17" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
         <v>3.65</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
         <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
         <v>4.5</v>
@@ -5444,7 +5444,7 @@
         <v>4.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -5459,7 +5459,7 @@
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.43</v>
@@ -5471,7 +5471,7 @@
         <v>2.02</v>
       </c>
       <c r="T20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U20" t="n">
         <v>3.05</v>
@@ -5495,7 +5495,7 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
@@ -5507,13 +5507,13 @@
         <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI20" t="n">
         <v>70</v>
@@ -5522,7 +5522,7 @@
         <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL20" t="n">
         <v>32</v>
@@ -5534,7 +5534,7 @@
         <v>6.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
@@ -5543,7 +5543,7 @@
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AS20" t="n">
         <v>36</v>
@@ -5579,7 +5579,7 @@
         <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE20" t="n">
         <v>36</v>
@@ -5588,7 +5588,7 @@
         <v>5.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="n">
         <v>5.6</v>
@@ -5600,7 +5600,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5648,11 +5648,11 @@
         <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G21" t="n">
         <v>1.83</v>
@@ -5698,7 +5698,7 @@
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.35</v>
@@ -5707,7 +5707,7 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.26</v>
@@ -5716,16 +5716,16 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
         <v>2.92</v>
       </c>
       <c r="T21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
         <v>2.22</v>
@@ -5737,7 +5737,7 @@
         <v>2.2</v>
       </c>
       <c r="X21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
         <v>20</v>
@@ -5755,10 +5755,10 @@
         <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AF21" t="n">
         <v>11.5</v>
@@ -5770,7 +5770,7 @@
         <v>25</v>
       </c>
       <c r="AI21" t="n">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="AJ21" t="n">
         <v>19.5</v>
@@ -5788,16 +5788,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO21" t="n">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="AP21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AS21" t="n">
         <v>38</v>
@@ -5818,13 +5818,13 @@
         <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BB21" t="n">
         <v>16</v>
@@ -5833,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BE21" t="n">
         <v>38</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5946,13 +5946,13 @@
         <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
         <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.23</v>
@@ -5967,7 +5967,7 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
         <v>1.52</v>
@@ -5976,7 +5976,7 @@
         <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T22" t="n">
         <v>1.5</v>
@@ -5985,13 +5985,13 @@
         <v>2.66</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
         <v>1.81</v>
       </c>
       <c r="X22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y22" t="n">
         <v>25</v>
@@ -6066,7 +6066,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX22" t="n">
         <v>12.5</v>
@@ -6090,7 +6090,7 @@
         <v>19</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF22" t="n">
         <v>6.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R23" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G24" t="n">
         <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
         <v>3.55</v>
@@ -6466,7 +6466,7 @@
         <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
         <v>3.75</v>
@@ -6487,7 +6487,7 @@
         <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
         <v>2.16</v>
@@ -6496,10 +6496,10 @@
         <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X24" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
         <v>13.5</v>
@@ -6508,7 +6508,7 @@
         <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AB24" t="n">
         <v>11</v>
@@ -6520,7 +6520,7 @@
         <v>17.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -6544,13 +6544,13 @@
         <v>50</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -6559,10 +6559,10 @@
         <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
@@ -6574,37 +6574,37 @@
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BH24" t="n">
         <v>3.45</v>
@@ -6628,7 +6628,7 @@
         <v>5.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
@@ -6649,7 +6649,7 @@
         <v>4.9</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW24" t="n">
         <v>9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         <v>3.25</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
         <v>1.31</v>
@@ -6977,13 +6977,13 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
         <v>1.86</v>
@@ -7001,7 +7001,7 @@
         <v>2.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
         <v>1.64</v>
@@ -7013,10 +7013,10 @@
         <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB26" t="n">
         <v>12.5</v>
@@ -7037,28 +7037,28 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="n">
         <v>60</v>
       </c>
       <c r="AK26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL26" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO26" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AP26" t="n">
         <v>14</v>
@@ -7067,7 +7067,7 @@
         <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AS26" t="n">
         <v>34</v>
@@ -7082,7 +7082,7 @@
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX26" t="n">
         <v>14.5</v>
@@ -7094,19 +7094,19 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
         <v>26</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF26" t="n">
         <v>16</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7234,19 +7234,19 @@
         <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
         <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T27" t="n">
         <v>1.03</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -7485,13 +7485,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="O28" t="n">
         <v>1.16</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
         <v>1.16</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7975,16 +7975,16 @@
         <v>3.5</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I30" t="n">
         <v>2.32</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.39</v>
@@ -8002,7 +8002,7 @@
         <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R30" t="n">
         <v>1.41</v>
@@ -8011,10 +8011,10 @@
         <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U30" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V30" t="n">
         <v>1.75</v>
@@ -8047,7 +8047,7 @@
         <v>28</v>
       </c>
       <c r="AF30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG30" t="n">
         <v>14.5</v>
@@ -8086,7 +8086,7 @@
         <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT30" t="n">
         <v>12.5</v>
@@ -8110,19 +8110,19 @@
         <v>14.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BD30" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF30" t="n">
         <v>24</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G31" t="n">
         <v>3.05</v>
       </c>
       <c r="H31" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -8265,13 +8265,13 @@
         <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W31" t="n">
         <v>1.48</v>
@@ -8286,7 +8286,7 @@
         <v>19</v>
       </c>
       <c r="AA31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB31" t="n">
         <v>13.5</v>
@@ -8352,7 +8352,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX31" t="n">
         <v>17.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         <v>7.4</v>
       </c>
       <c r="H32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I32" t="n">
         <v>1.53</v>
@@ -8516,7 +8516,7 @@
         <v>1.88</v>
       </c>
       <c r="S32" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="T32" t="n">
         <v>1.59</v>
@@ -8534,7 +8534,7 @@
         <v>44</v>
       </c>
       <c r="Y32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z32" t="n">
         <v>15.5</v>
@@ -8588,7 +8588,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR32" t="n">
         <v>10</v>
@@ -8642,7 +8642,7 @@
         <v>5.4</v>
       </c>
       <c r="BI32" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ32" t="n">
         <v>9.4</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>2.22</v>
       </c>
       <c r="J34" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
@@ -9009,7 +9009,7 @@
         <v>1.04</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>1.22</v>
@@ -9030,13 +9030,13 @@
         <v>1.6</v>
       </c>
       <c r="U34" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V34" t="n">
         <v>1.82</v>
       </c>
       <c r="W34" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X34" t="n">
         <v>27</v>
@@ -9063,10 +9063,10 @@
         <v>25</v>
       </c>
       <c r="AF34" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AG34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH34" t="n">
         <v>19</v>
@@ -9078,22 +9078,22 @@
         <v>60</v>
       </c>
       <c r="AK34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL34" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM34" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ34" t="n">
         <v>11.5</v>
@@ -9129,40 +9129,40 @@
         <v>20</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF34" t="n">
         <v>18.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH34" t="n">
         <v>4.2</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK34" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN34" t="n">
         <v>7.2</v>
@@ -9174,28 +9174,28 @@
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR34" t="n">
         <v>32</v>
       </c>
       <c r="BS34" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT34" t="n">
         <v>5.3</v>
       </c>
       <c r="BU34" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BV34" t="n">
         <v>14</v>
       </c>
       <c r="BW34" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY34" t="n">
         <v>9.199999999999999</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -9239,19 +9239,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G35" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I35" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>4.4</v>
@@ -9266,31 +9266,31 @@
         <v>4.6</v>
       </c>
       <c r="O35" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P35" t="n">
         <v>2.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R35" t="n">
         <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W35" t="n">
         <v>2.22</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.26</v>
       </c>
       <c r="X35" t="n">
         <v>24</v>
@@ -9299,10 +9299,10 @@
         <v>25</v>
       </c>
       <c r="Z35" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA35" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB35" t="n">
         <v>10.5</v>
@@ -9311,25 +9311,25 @@
         <v>9.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE35" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF35" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG35" t="n">
         <v>10.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI35" t="n">
         <v>70</v>
       </c>
       <c r="AJ35" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK35" t="n">
         <v>18</v>
@@ -9338,13 +9338,13 @@
         <v>32</v>
       </c>
       <c r="AM35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN35" t="n">
         <v>9</v>
       </c>
       <c r="AO35" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP35" t="n">
         <v>17</v>
@@ -9353,22 +9353,22 @@
         <v>17</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AS35" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT35" t="n">
         <v>9.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV35" t="n">
         <v>16.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX35" t="n">
         <v>10</v>
@@ -9380,34 +9380,34 @@
         <v>16</v>
       </c>
       <c r="BA35" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB35" t="n">
         <v>15.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG35" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH35" t="n">
         <v>4.1</v>
       </c>
       <c r="BI35" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BJ35" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK35" t="n">
         <v>5</v>
@@ -9416,7 +9416,7 @@
         <v>110</v>
       </c>
       <c r="BM35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN35" t="n">
         <v>4.8</v>
@@ -9428,7 +9428,7 @@
         <v>12</v>
       </c>
       <c r="BQ35" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR35" t="n">
         <v>24</v>
@@ -9452,7 +9452,7 @@
         <v>44</v>
       </c>
       <c r="BY35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ35" t="n">
         <v>18</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9517,22 +9517,22 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O36" t="n">
         <v>1.07</v>
       </c>
       <c r="P36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q36" t="n">
         <v>1.07</v>
       </c>
       <c r="R36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9601,52 +9601,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G37" t="n">
         <v>1.36</v>
@@ -9756,13 +9756,13 @@
         <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
         <v>5.7</v>
       </c>
       <c r="K37" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.26</v>
@@ -9771,7 +9771,7 @@
         <v>1.03</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>1.21</v>
@@ -9783,46 +9783,46 @@
         <v>1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S37" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T37" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V37" t="n">
         <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X37" t="n">
         <v>28</v>
       </c>
       <c r="Y37" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Z37" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA37" t="n">
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC37" t="n">
         <v>14.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AE37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AF37" t="n">
         <v>8.6</v>
@@ -9831,10 +9831,10 @@
         <v>11</v>
       </c>
       <c r="AH37" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI37" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ37" t="n">
         <v>11</v>
@@ -9843,28 +9843,28 @@
         <v>15</v>
       </c>
       <c r="AL37" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM37" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN37" t="n">
         <v>5.1</v>
       </c>
       <c r="AO37" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP37" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR37" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT37" t="n">
         <v>8.199999999999999</v>
@@ -9873,22 +9873,22 @@
         <v>11.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AW37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB37" t="n">
         <v>9.6</v>
@@ -9897,22 +9897,22 @@
         <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF37" t="n">
         <v>4.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH37" t="n">
         <v>4.4</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BJ37" t="n">
         <v>13</v>
@@ -9924,10 +9924,10 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO37" t="n">
         <v>3.1</v>
@@ -9942,35 +9942,35 @@
         <v>24</v>
       </c>
       <c r="BS37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT37" t="n">
         <v>15</v>
       </c>
       <c r="BU37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ37" t="n">
         <v>12</v>
       </c>
       <c r="CA37" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -10763,19 +10763,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="I41" t="n">
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -11020,16 +11020,16 @@
         <v>1.65</v>
       </c>
       <c r="G42" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K42" t="n">
         <v>5.2</v>
@@ -11047,7 +11047,7 @@
         <v>1.15</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="Q42" t="n">
         <v>1.46</v>
@@ -11074,7 +11074,7 @@
         <v>38</v>
       </c>
       <c r="Y42" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z42" t="n">
         <v>55</v>
@@ -11086,7 +11086,7 @@
         <v>15.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD42" t="n">
         <v>21</v>
@@ -11107,7 +11107,7 @@
         <v>55</v>
       </c>
       <c r="AJ42" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
         <v>16.5</v>
@@ -11119,128 +11119,128 @@
         <v>75</v>
       </c>
       <c r="AN42" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO42" t="n">
         <v>42</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="BG42" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BH42" t="n">
         <v>5.1</v>
       </c>
       <c r="BI42" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BJ42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK42" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN42" t="n">
         <v>5.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BP42" t="n">
         <v>11</v>
       </c>
       <c r="BQ42" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR42" t="n">
         <v>20</v>
       </c>
       <c r="BS42" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BT42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU42" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="BZ42" t="n">
         <v>12.5</v>
       </c>
       <c r="CA42" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G44" t="n">
         <v>2.06</v>
@@ -11534,10 +11534,10 @@
         <v>3.7</v>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J44" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K44" t="n">
         <v>4.5</v>
@@ -11555,7 +11555,7 @@
         <v>1.2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q44" t="n">
         <v>1.59</v>
@@ -11573,7 +11573,7 @@
         <v>2.42</v>
       </c>
       <c r="V44" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W44" t="n">
         <v>1.94</v>
@@ -11591,7 +11591,7 @@
         <v>85</v>
       </c>
       <c r="AB44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC44" t="n">
         <v>12</v>
@@ -11615,7 +11615,7 @@
         <v>50</v>
       </c>
       <c r="AJ44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK44" t="n">
         <v>23</v>
@@ -11627,7 +11627,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO44" t="n">
         <v>36</v>
@@ -11708,7 +11708,7 @@
         <v>5.3</v>
       </c>
       <c r="BO44" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP44" t="n">
         <v>13.5</v>
@@ -11726,7 +11726,7 @@
         <v>7.8</v>
       </c>
       <c r="BU44" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11797,7 @@
         <v>3.8</v>
       </c>
       <c r="L45" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -11818,7 +11818,7 @@
         <v>1.23</v>
       </c>
       <c r="S45" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T45" t="n">
         <v>2</v>
@@ -11887,64 +11887,64 @@
         <v>160</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF45" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH45" t="n">
         <v>3.1</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="BJ45" t="n">
         <v>11.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -12296,16 +12296,16 @@
         <v>1.91</v>
       </c>
       <c r="I47" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>3.6</v>
       </c>
       <c r="K47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L47" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M47" t="n">
         <v>1.05</v>
@@ -12326,16 +12326,16 @@
         <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U47" t="n">
         <v>2.18</v>
       </c>
       <c r="V47" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W47" t="n">
         <v>1.29</v>
@@ -12356,7 +12356,7 @@
         <v>22</v>
       </c>
       <c r="AC47" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD47" t="n">
         <v>13</v>
@@ -12398,7 +12398,7 @@
         <v>13</v>
       </c>
       <c r="AQ47" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AR47" t="n">
         <v>10</v>
@@ -12413,7 +12413,7 @@
         <v>6.6</v>
       </c>
       <c r="AV47" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW47" t="n">
         <v>14.5</v>
@@ -12446,61 +12446,61 @@
         <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH47" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI47" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ47" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK47" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN47" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO47" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP47" t="n">
         <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR47" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS47" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT47" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU47" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV47" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW47" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ47" t="n">
         <v>0</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -12795,190 +12795,190 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G49" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J49" t="n">
         <v>3.05</v>
-      </c>
-      <c r="I49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.1</v>
       </c>
       <c r="K49" t="n">
         <v>3.55</v>
       </c>
       <c r="L49" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M49" t="n">
         <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O49" t="n">
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R49" t="n">
         <v>1.24</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U49" t="n">
         <v>1.91</v>
       </c>
       <c r="V49" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W49" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X49" t="n">
         <v>12.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA49" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB49" t="n">
         <v>10.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE49" t="n">
         <v>55</v>
       </c>
       <c r="AF49" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG49" t="n">
         <v>14</v>
       </c>
       <c r="AH49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI49" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ49" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL49" t="n">
         <v>60</v>
       </c>
       <c r="AM49" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN49" t="n">
         <v>36</v>
       </c>
       <c r="AO49" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP49" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR49" t="n">
         <v>17.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT49" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU49" t="n">
         <v>5.9</v>
       </c>
       <c r="AV49" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="AX49" t="n">
         <v>11.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA49" t="n">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="BB49" t="n">
-        <v>28</v>
+        <v>4.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>38</v>
+        <v>4.6</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.8</v>
+        <v>22</v>
       </c>
       <c r="BG49" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BH49" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI49" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ49" t="n">
         <v>11</v>
       </c>
       <c r="BK49" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN49" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO49" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP49" t="n">
         <v>21</v>
@@ -12990,19 +12990,19 @@
         <v>40</v>
       </c>
       <c r="BS49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT49" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU49" t="n">
         <v>5</v>
       </c>
       <c r="BV49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX49" t="n">
         <v>48</v>
@@ -13014,11 +13014,11 @@
         <v>40</v>
       </c>
       <c r="CA49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -13049,40 +13049,40 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="G50" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>3.5</v>
       </c>
       <c r="K50" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L50" t="n">
         <v>1.38</v>
       </c>
       <c r="M50" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O50" t="n">
         <v>1.37</v>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="R50" t="n">
         <v>1.29</v>
@@ -13091,40 +13091,40 @@
         <v>3.85</v>
       </c>
       <c r="T50" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U50" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V50" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W50" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X50" t="n">
         <v>14.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB50" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="n">
         <v>13.5</v>
@@ -13133,28 +13133,28 @@
         <v>12</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN50" t="n">
         <v>18.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP50" t="n">
         <v>10.5</v>
@@ -13163,10 +13163,10 @@
         <v>12.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT50" t="n">
         <v>6.8</v>
@@ -13178,7 +13178,7 @@
         <v>16</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX50" t="n">
         <v>9.6</v>
@@ -13190,7 +13190,7 @@
         <v>17.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB50" t="n">
         <v>19</v>
@@ -13199,16 +13199,16 @@
         <v>18.5</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF50" t="n">
         <v>12</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH50" t="n">
         <v>3.35</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -13294,187 +13294,187 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="H51" t="n">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="J51" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K51" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L51" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M51" t="n">
         <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R51" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S51" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U51" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="V51" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="W51" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="X51" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD51" t="n">
         <v>13</v>
       </c>
-      <c r="Y51" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="AE51" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ51" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC51" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AR51" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AS51" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT51" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU51" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV51" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX51" t="n">
         <v>16</v>
       </c>
-      <c r="AW51" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>10</v>
-      </c>
       <c r="AY51" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ51" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC51" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB51" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>21</v>
-      </c>
       <c r="BD51" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE51" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="BG51" t="n">
         <v>4.9</v>
       </c>
       <c r="BH51" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK51" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
@@ -13483,50 +13483,50 @@
         <v>14.5</v>
       </c>
       <c r="BN51" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO51" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP51" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="BQ51" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BR51" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS51" t="n">
         <v>11</v>
       </c>
       <c r="BT51" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU51" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV51" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW51" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ51" t="n">
         <v>34</v>
       </c>
       <c r="CA51" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -13548,239 +13548,239 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.74</v>
+        <v>2.06</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="H52" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J52" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L52" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
       </c>
       <c r="N52" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O52" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P52" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R52" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V52" t="n">
         <v>1.27</v>
       </c>
-      <c r="S52" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U52" t="n">
-        <v>2</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W52" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="X52" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF52" t="n">
         <v>12</v>
       </c>
-      <c r="Z52" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="AG52" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ52" t="n">
         <v>12</v>
       </c>
-      <c r="AC52" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP52" t="n">
+      <c r="AR52" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX52" t="n">
         <v>10</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>13.5</v>
       </c>
       <c r="AY52" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BB52" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BC52" t="n">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="BD52" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF52" t="n">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="BG52" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BH52" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU52" t="n">
         <v>6</v>
       </c>
-      <c r="BL52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM52" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ52" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR52" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS52" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT52" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU52" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BV52" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BW52" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BX52" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BY52" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ52" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA52" t="n">
         <v>10.5</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -13850,16 +13850,16 @@
         <v>1.24</v>
       </c>
       <c r="S53" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T53" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="U53" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="V53" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W53" t="n">
         <v>1.53</v>
@@ -13880,7 +13880,7 @@
         <v>11</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD53" t="n">
         <v>17</v>
@@ -13919,58 +13919,58 @@
         <v>60</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF53" t="n">
-        <v>24</v>
+        <v>4.1</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH53" t="n">
         <v>3.1</v>
@@ -13994,7 +13994,7 @@
         <v>5.7</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP53" t="n">
         <v>23</v>
@@ -14012,7 +14012,7 @@
         <v>6.4</v>
       </c>
       <c r="BU53" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BV53" t="n">
         <v>29</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
         <v>4.1</v>
       </c>
       <c r="G54" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="H54" t="n">
         <v>1.77</v>
@@ -14083,13 +14083,13 @@
         <v>4.5</v>
       </c>
       <c r="L54" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M54" t="n">
         <v>1.05</v>
       </c>
       <c r="N54" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O54" t="n">
         <v>1.26</v>
@@ -14119,58 +14119,58 @@
         <v>1.26</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA54" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB54" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC54" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD54" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF54" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG54" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH54" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI54" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL54" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO54" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP54" t="n">
         <v>1.03</v>
@@ -14227,16 +14227,16 @@
         <v>8</v>
       </c>
       <c r="BH54" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ54" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
@@ -14245,16 +14245,16 @@
         <v>1.01</v>
       </c>
       <c r="BN54" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO54" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BP54" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
@@ -14263,32 +14263,32 @@
         <v>1.01</v>
       </c>
       <c r="BT54" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV54" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX54" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ54" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -14334,13 +14334,13 @@
         <v>2.86</v>
       </c>
       <c r="K55" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L55" t="n">
         <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N55" t="n">
         <v>2.34</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -14576,13 +14576,13 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H56" t="n">
         <v>3.55</v>
       </c>
       <c r="I56" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>2.74</v>
@@ -14606,13 +14606,13 @@
         <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R56" t="n">
         <v>1.21</v>
       </c>
       <c r="S56" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="T56" t="n">
         <v>2</v>
@@ -14621,7 +14621,7 @@
         <v>1.79</v>
       </c>
       <c r="V56" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W56" t="n">
         <v>1.73</v>
@@ -14681,64 +14681,64 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AQ56" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR56" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AS56" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AV56" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="AX56" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AY56" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AZ56" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.9</v>
+        <v>2.88</v>
       </c>
       <c r="BB56" t="n">
-        <v>4.4</v>
+        <v>2.72</v>
       </c>
       <c r="BC56" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.7</v>
+        <v>2.82</v>
       </c>
       <c r="BE56" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="BG56" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="BH56" t="n">
         <v>1000</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -14839,13 +14839,13 @@
         <v>5.3</v>
       </c>
       <c r="J57" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K57" t="n">
         <v>4.1</v>
       </c>
       <c r="L57" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="n">
         <v>1.07</v>
@@ -14857,22 +14857,22 @@
         <v>1.31</v>
       </c>
       <c r="P57" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="R57" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S57" t="n">
         <v>3.1</v>
       </c>
       <c r="T57" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U57" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V57" t="n">
         <v>1.23</v>
@@ -14881,7 +14881,7 @@
         <v>1.9</v>
       </c>
       <c r="X57" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y57" t="n">
         <v>18</v>
@@ -14893,40 +14893,40 @@
         <v>110</v>
       </c>
       <c r="AB57" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD57" t="n">
         <v>21</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF57" t="n">
         <v>14</v>
       </c>
       <c r="AG57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH57" t="n">
         <v>22</v>
       </c>
       <c r="AI57" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK57" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL57" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM57" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN57" t="n">
         <v>16.5</v>
@@ -14935,58 +14935,58 @@
         <v>75</v>
       </c>
       <c r="AP57" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AR57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY57" t="n">
         <v>3.6</v>
       </c>
-      <c r="AS57" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AZ57" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BA57" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BB57" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC57" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="BG57" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH57" t="n">
         <v>3.55</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15102,7 @@
         <v>1.47</v>
       </c>
       <c r="M58" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N58" t="n">
         <v>2.6</v>
@@ -15120,7 +15120,7 @@
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T58" t="n">
         <v>2.04</v>
@@ -15135,46 +15135,46 @@
         <v>1.64</v>
       </c>
       <c r="X58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA58" t="n">
         <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI58" t="n">
         <v>110</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK58" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL58" t="n">
         <v>75</v>
@@ -15183,64 +15183,64 @@
         <v>1000</v>
       </c>
       <c r="AN58" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO58" t="n">
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BH58" t="n">
         <v>1000</v>
@@ -15304,14 +15304,14 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15326,127 +15326,127 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="G59" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="H59" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K59" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L59" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M59" t="n">
         <v>1.05</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O59" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P59" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R59" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S59" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="U59" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="V59" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="W59" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="X59" t="n">
         <v>20</v>
       </c>
       <c r="Y59" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ59" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z59" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>24</v>
-      </c>
       <c r="AK59" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL59" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM59" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AN59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO59" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AR59" t="n">
         <v>1.03</v>
@@ -15455,34 +15455,34 @@
         <v>1.03</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV59" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW59" t="n">
         <v>1.03</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ59" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA59" t="n">
         <v>1.03</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD59" t="n">
         <v>1.03</v>
@@ -15491,22 +15491,22 @@
         <v>1.03</v>
       </c>
       <c r="BF59" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG59" t="n">
-        <v>9.199999999999999</v>
+        <v>85</v>
       </c>
       <c r="BH59" t="n">
         <v>3.8</v>
       </c>
       <c r="BI59" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ59" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BK59" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
@@ -15515,50 +15515,50 @@
         <v>1.01</v>
       </c>
       <c r="BN59" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BP59" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BQ59" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BR59" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS59" t="n">
         <v>19</v>
       </c>
       <c r="BT59" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BU59" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BV59" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ59" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA59" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G60" t="n">
         <v>2.36</v>
@@ -15598,7 +15598,7 @@
         <v>3.85</v>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>3.05</v>
@@ -15610,7 +15610,7 @@
         <v>1.46</v>
       </c>
       <c r="M60" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N60" t="n">
         <v>2.68</v>
@@ -15628,7 +15628,7 @@
         <v>1.2</v>
       </c>
       <c r="S60" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T60" t="n">
         <v>2.08</v>
@@ -15637,13 +15637,13 @@
         <v>1.8</v>
       </c>
       <c r="V60" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W60" t="n">
         <v>1.73</v>
       </c>
       <c r="X60" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y60" t="n">
         <v>13.5</v>
@@ -15655,13 +15655,13 @@
         <v>120</v>
       </c>
       <c r="AB60" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC60" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE60" t="n">
         <v>80</v>
@@ -15688,7 +15688,7 @@
         <v>70</v>
       </c>
       <c r="AM60" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN60" t="n">
         <v>36</v>
@@ -15697,16 +15697,16 @@
         <v>120</v>
       </c>
       <c r="AP60" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ60" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR60" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT60" t="n">
         <v>6.4</v>
@@ -15718,37 +15718,37 @@
         <v>15</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX60" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AY60" t="n">
         <v>10</v>
       </c>
       <c r="AZ60" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BA60" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB60" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BC60" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF60" t="n">
         <v>21</v>
       </c>
       <c r="BG60" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH60" t="n">
         <v>2.8</v>
@@ -15812,14 +15812,14 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15834,85 +15834,85 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="G61" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="H61" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="I61" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J61" t="n">
         <v>3.5</v>
       </c>
-      <c r="J61" t="n">
-        <v>2.88</v>
-      </c>
       <c r="K61" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L61" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M61" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N61" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="O61" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="P61" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="R61" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S61" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="T61" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="U61" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="V61" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W61" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="X61" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Y61" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z61" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA61" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB61" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC61" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD61" t="n">
         <v>17.5</v>
@@ -15921,34 +15921,34 @@
         <v>55</v>
       </c>
       <c r="AF61" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG61" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH61" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ61" t="n">
         <v>24</v>
       </c>
-      <c r="AI61" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ61" t="n">
+      <c r="AK61" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL61" t="n">
         <v>48</v>
       </c>
-      <c r="AK61" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>65</v>
-      </c>
       <c r="AM61" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AN61" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO61" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP61" t="n">
         <v>1.03</v>
@@ -15999,81 +15999,81 @@
         <v>1.03</v>
       </c>
       <c r="BF61" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH61" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="BJ61" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK61" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BN61" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BO61" t="n">
         <v>3.8</v>
       </c>
       <c r="BP61" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BQ61" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="BR61" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BS61" t="n">
-        <v>2.3</v>
+        <v>21</v>
       </c>
       <c r="BT61" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU61" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV61" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BW61" t="n">
-        <v>2.26</v>
+        <v>25</v>
       </c>
       <c r="BX61" t="n">
         <v>46</v>
       </c>
       <c r="BY61" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ61" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA61" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16083,244 +16083,244 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.51</v>
+        <v>2.44</v>
       </c>
       <c r="G62" t="n">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="H62" t="n">
-        <v>6.8</v>
+        <v>2.94</v>
       </c>
       <c r="I62" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="K62" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="L62" t="n">
         <v>1.4</v>
       </c>
       <c r="M62" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O62" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="P62" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="R62" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S62" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X62" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY62" t="n">
         <v>3.3</v>
       </c>
-      <c r="T62" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W62" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X62" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP62" t="n">
+      <c r="AZ62" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG62" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ62" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC62" t="n">
+      <c r="BH62" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ62" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU62" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD62" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI62" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ62" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK62" t="n">
-        <v>9</v>
-      </c>
-      <c r="BL62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN62" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO62" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP62" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ62" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR62" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS62" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT62" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU62" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BV62" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW62" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BX62" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY62" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BZ62" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA62" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -16342,246 +16342,246 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="H63" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="I63" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K63" t="n">
         <v>4.7</v>
       </c>
-      <c r="J63" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S63" t="n">
         <v>3.45</v>
       </c>
-      <c r="L63" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.82</v>
-      </c>
       <c r="T63" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U63" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V63" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="W63" t="n">
-        <v>1.73</v>
+        <v>2.56</v>
       </c>
       <c r="X63" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC63" t="n">
         <v>11</v>
       </c>
-      <c r="Y63" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z63" t="n">
+      <c r="AD63" t="n">
         <v>34</v>
       </c>
-      <c r="AA63" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD63" t="n">
+      <c r="AE63" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK63" t="n">
         <v>21</v>
       </c>
-      <c r="AE63" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>36</v>
-      </c>
       <c r="AL63" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM63" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN63" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AO63" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF63" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH63" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="BI63" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM63" t="n">
         <v>2.5</v>
       </c>
-      <c r="BJ63" t="n">
+      <c r="BN63" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT63" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK63" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BU63" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BV63" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW63" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA63" t="n">
         <v>6.6</v>
       </c>
-      <c r="BX63" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>0</v>
-      </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16591,234 +16591,234 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.55</v>
+        <v>2.08</v>
       </c>
       <c r="G64" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="H64" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="I64" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X64" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX64" t="n">
         <v>3.75</v>
       </c>
-      <c r="K64" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>0</v>
-      </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA64" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG64" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH64" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BI64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ64" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK64" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BN64" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP64" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BQ64" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BT64" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU64" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV64" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW64" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BX64" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BY64" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BZ64" t="n">
         <v>0</v>
@@ -16828,7 +16828,261 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7</v>
+      </c>
+      <c r="I65" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB65" t="inlineStr">
+        <is>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
         <v>2.06</v>
@@ -869,7 +869,7 @@
         <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
@@ -965,10 +965,10 @@
         <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AR2" t="n">
         <v>4.7</v>
@@ -977,22 +977,22 @@
         <v>4.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW2" t="n">
         <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AZ2" t="n">
         <v>4.3</v>
@@ -1001,7 +1001,7 @@
         <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
         <v>4.4</v>
@@ -1013,7 +1013,7 @@
         <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG2" t="n">
         <v>4.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>3.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -1129,7 +1129,7 @@
         <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
@@ -1153,7 +1153,7 @@
         <v>5.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
         <v>1.84</v>
@@ -1162,7 +1162,7 @@
         <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
         <v>9</v>
@@ -1171,13 +1171,13 @@
         <v>8.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
         <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>7</v>
@@ -1189,7 +1189,7 @@
         <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1201,7 +1201,7 @@
         <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="AK3" t="n">
         <v>48</v>
@@ -1216,13 +1216,13 @@
         <v>60</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
@@ -1246,19 +1246,19 @@
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD3" t="n">
         <v>34</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,7 +1392,7 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
         <v>1.75</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
         <v>2.48</v>
@@ -1643,28 +1643,28 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
@@ -1694,7 +1694,7 @@
         <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF5" t="n">
         <v>14</v>
@@ -1715,7 +1715,7 @@
         <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1730,10 +1730,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
         <v>32</v>
@@ -1745,7 +1745,7 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
         <v>27</v>
@@ -1763,7 +1763,7 @@
         <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>44</v>
@@ -2271,19 +2271,19 @@
         <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
         <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.1</v>
       </c>
       <c r="BG7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2764,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
         <v>16</v>
@@ -2782,7 +2782,7 @@
         <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD9" t="n">
         <v>4.7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2895,16 @@
         <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2916,28 +2916,28 @@
         <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
         <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
         <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
         <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
         <v>1.45</v>
@@ -2946,7 +2946,7 @@
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
         <v>17.5</v>
@@ -2958,7 +2958,7 @@
         <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
         <v>12</v>
@@ -2988,7 +2988,7 @@
         <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AN10" t="n">
         <v>22</v>
@@ -2997,19 +2997,19 @@
         <v>13.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
         <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8.199999999999999</v>
@@ -3030,7 +3030,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
         <v>28</v>
@@ -3039,13 +3039,13 @@
         <v>19.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE10" t="n">
         <v>30</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG10" t="n">
         <v>11.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         <v>3.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV11" t="n">
         <v>4.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="K12" t="n">
         <v>7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.85</v>
@@ -3726,7 +3726,7 @@
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -3756,16 +3756,16 @@
         <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ13" t="n">
         <v>9</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS13" t="n">
         <v>4.6</v>
@@ -3789,7 +3789,7 @@
         <v>3.65</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA13" t="n">
         <v>4.6</v>
@@ -3798,7 +3798,7 @@
         <v>4.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD13" t="n">
         <v>4.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.48</v>
@@ -3986,10 +3986,10 @@
         <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>120</v>
@@ -3998,7 +3998,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
@@ -4037,7 +4037,7 @@
         <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
@@ -4055,7 +4055,7 @@
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>6.4</v>
@@ -4073,62 +4073,62 @@
         <v>2.4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>3.75</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
@@ -4201,7 +4201,7 @@
         <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
         <v>1.96</v>
@@ -4270,7 +4270,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
@@ -4279,13 +4279,13 @@
         <v>6.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU15" t="n">
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW15" t="n">
         <v>6.2</v>
@@ -4294,7 +4294,7 @@
         <v>4.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>16.5</v>
@@ -4312,7 +4312,7 @@
         <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
         <v>5.2</v>
@@ -4330,7 +4330,7 @@
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,10 +4342,10 @@
         <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ15" t="n">
         <v>6.8</v>
@@ -4354,13 +4354,13 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT15" t="n">
         <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4372,17 +4372,17 @@
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4422,13 +4422,13 @@
         <v>3.65</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>1.37</v>
@@ -4443,19 +4443,19 @@
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U16" t="n">
         <v>2.06</v>
@@ -4473,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
         <v>95</v>
@@ -4482,7 +4482,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
         <v>16</v>
@@ -4497,7 +4497,7 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
         <v>70</v>
@@ -4527,10 +4527,10 @@
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>8</v>
@@ -4542,7 +4542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
         <v>12</v>
@@ -4554,25 +4554,25 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC16" t="n">
         <v>21</v>
       </c>
       <c r="BD16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
         <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>3.25</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
         <v>1.78</v>
@@ -4778,7 +4778,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
         <v>7.2</v>
@@ -4826,7 +4826,7 @@
         <v>5.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BH17" t="n">
         <v>3.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>2.9</v>
@@ -4954,7 +4954,7 @@
         <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
         <v>1.2</v>
@@ -4969,7 +4969,7 @@
         <v>1.78</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
         <v>1.59</v>
@@ -4990,7 +4990,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -5014,7 +5014,7 @@
         <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
         <v>65</v>
@@ -5023,64 +5023,64 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO18" t="n">
         <v>95</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AR18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD18" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC18" t="n">
+      <c r="BE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.2</v>
       </c>
       <c r="BH18" t="n">
         <v>2.94</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
         <v>3.75</v>
@@ -5199,10 +5199,10 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
@@ -5214,19 +5214,19 @@
         <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5238,7 +5238,7 @@
         <v>970</v>
       </c>
       <c r="AA19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
         <v>970</v>
@@ -5250,7 +5250,7 @@
         <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
         <v>32</v>
@@ -5277,64 +5277,64 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AW19" t="n">
         <v>2.06</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.7</v>
+        <v>2.06</v>
       </c>
       <c r="AY19" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G20" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I20" t="n">
         <v>4.2</v>
@@ -5447,7 +5447,7 @@
         <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
@@ -5456,7 +5456,7 @@
         <v>7.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
         <v>3.15</v>
@@ -5480,7 +5480,7 @@
         <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
         <v>80</v>
@@ -5489,7 +5489,7 @@
         <v>30</v>
       </c>
       <c r="Z20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -5504,46 +5504,46 @@
         <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
         <v>65</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
         <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
         <v>18.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AS20" t="n">
         <v>36</v>
@@ -5555,25 +5555,25 @@
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
         <v>22</v>
       </c>
       <c r="BB20" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BC20" t="n">
         <v>12.5</v>
@@ -5582,16 +5582,16 @@
         <v>16.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BF20" t="n">
         <v>6</v>
       </c>
       <c r="BG20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI20" t="n">
         <v>4.1</v>
@@ -5600,31 +5600,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN20" t="n">
         <v>5.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR20" t="n">
         <v>19</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT20" t="n">
         <v>8.4</v>
@@ -5636,23 +5636,23 @@
         <v>26</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ20" t="n">
         <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
         <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
         <v>1.77</v>
@@ -5734,7 +5734,7 @@
         <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
         <v>20</v>
@@ -5767,7 +5767,7 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
@@ -5809,7 +5809,7 @@
         <v>8.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
         <v>29</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ22" t="n">
         <v>2.68</v>
@@ -6084,7 +6084,7 @@
         <v>5.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD22" t="n">
         <v>2.58</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>3.75</v>
       </c>
       <c r="L23" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -6233,7 +6233,7 @@
         <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U23" t="n">
         <v>2.16</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I24" t="n">
         <v>3.25</v>
@@ -6475,7 +6475,7 @@
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
         <v>1.85</v>
@@ -6490,13 +6490,13 @@
         <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
         <v>1.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X24" t="n">
         <v>16.5</v>
@@ -6505,10 +6505,10 @@
         <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
@@ -6517,19 +6517,19 @@
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI24" t="n">
         <v>100</v>
@@ -6538,7 +6538,7 @@
         <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AL24" t="n">
         <v>80</v>
@@ -6547,10 +6547,10 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
         <v>14</v>
@@ -6562,13 +6562,13 @@
         <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
         <v>12</v>
@@ -6586,7 +6586,7 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BB24" t="n">
         <v>21</v>
@@ -6622,7 +6622,7 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN24" t="n">
         <v>5.5</v>
@@ -6631,7 +6631,7 @@
         <v>4.9</v>
       </c>
       <c r="BP24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ24" t="n">
         <v>8.4</v>
@@ -6658,7 +6658,7 @@
         <v>34</v>
       </c>
       <c r="BY24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>1.23</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
         <v>5.9</v>
@@ -6989,16 +6989,16 @@
         <v>1.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S26" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T26" t="n">
         <v>1.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V26" t="n">
         <v>1.37</v>
@@ -7019,7 +7019,7 @@
         <v>75</v>
       </c>
       <c r="AB26" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
         <v>11.5</v>
@@ -7067,10 +7067,10 @@
         <v>16.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT26" t="n">
         <v>12</v>
@@ -7082,7 +7082,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
         <v>12.5</v>
@@ -7094,10 +7094,10 @@
         <v>10.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
@@ -7106,7 +7106,7 @@
         <v>19</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF26" t="n">
         <v>6.8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
         <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
         <v>1.94</v>
@@ -7321,7 +7321,7 @@
         <v>4.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS27" t="n">
         <v>5.7</v>
@@ -7345,7 +7345,7 @@
         <v>4.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA27" t="n">
         <v>5.7</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>3.7</v>
       </c>
       <c r="H28" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I28" t="n">
         <v>2.4</v>
@@ -7476,7 +7476,7 @@
         <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.31</v>
@@ -7548,13 +7548,13 @@
         <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ28" t="n">
         <v>70</v>
       </c>
       <c r="AK28" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL28" t="n">
         <v>50</v>
@@ -7587,7 +7587,7 @@
         <v>1.46</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="AW28" t="n">
         <v>1.64</v>
@@ -7611,13 +7611,13 @@
         <v>1.47</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="BE28" t="n">
         <v>1.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.55</v>
+        <v>1.67</v>
       </c>
       <c r="BG28" t="n">
         <v>5.3</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>2.4</v>
       </c>
       <c r="G29" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H29" t="n">
         <v>3</v>
@@ -7727,13 +7727,13 @@
         <v>3.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
         <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -7742,7 +7742,7 @@
         <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
         <v>1.86</v>
@@ -7754,13 +7754,13 @@
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
         <v>1.42</v>
@@ -7832,13 +7832,13 @@
         <v>16.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.5</v>
+        <v>40</v>
       </c>
       <c r="AT29" t="n">
         <v>9</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
         <v>10.5</v>
@@ -7850,7 +7850,7 @@
         <v>12.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
         <v>13</v>
@@ -7874,7 +7874,7 @@
         <v>17.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>26</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="n">
         <v>3.35</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>2.28</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
         <v>3.7</v>
@@ -8005,7 +8005,7 @@
         <v>1.89</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
         <v>3.2</v>
@@ -8068,13 +8068,13 @@
         <v>55</v>
       </c>
       <c r="AM30" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
         <v>36</v>
       </c>
       <c r="AO30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>14</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>2.48</v>
       </c>
       <c r="I31" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -8271,7 +8271,7 @@
         <v>2.26</v>
       </c>
       <c r="V31" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W31" t="n">
         <v>1.48</v>
@@ -8340,7 +8340,7 @@
         <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8513,7 @@
         <v>1.38</v>
       </c>
       <c r="R32" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S32" t="n">
         <v>1.99</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>2.44</v>
       </c>
       <c r="I33" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="J33" t="n">
         <v>4.4</v>
@@ -8770,7 +8770,7 @@
         <v>2.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="T33" t="n">
         <v>1.32</v>
@@ -8785,7 +8785,7 @@
         <v>1.51</v>
       </c>
       <c r="X33" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Y33" t="n">
         <v>32</v>
@@ -8821,7 +8821,7 @@
         <v>28</v>
       </c>
       <c r="AJ33" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK33" t="n">
         <v>27</v>
@@ -8839,7 +8839,7 @@
         <v>10</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
         <v>21</v>
@@ -8890,7 +8890,7 @@
         <v>6.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="n">
         <v>6.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -9493,88 +9493,88 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I36" t="n">
         <v>2.7</v>
       </c>
-      <c r="G36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.6</v>
-      </c>
       <c r="J36" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
         <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R36" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S36" t="n">
         <v>2.34</v>
       </c>
       <c r="T36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V36" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W36" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="X36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y36" t="n">
         <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA36" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AB36" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC36" t="n">
         <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF36" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AG36" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH36" t="n">
         <v>17</v>
@@ -9583,82 +9583,82 @@
         <v>34</v>
       </c>
       <c r="AJ36" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL36" t="n">
         <v>32</v>
       </c>
-      <c r="AL36" t="n">
-        <v>38</v>
-      </c>
       <c r="AM36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN36" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AP36" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX36" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AY36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ36" t="n">
         <v>11</v>
       </c>
       <c r="BA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD36" t="n">
         <v>1.03</v>
       </c>
-      <c r="BB36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE36" t="n">
         <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ36" t="n">
         <v>8.800000000000001</v>
@@ -9673,10 +9673,10 @@
         <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO36" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BP36" t="n">
         <v>1000</v>
@@ -9691,10 +9691,10 @@
         <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU36" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>2.08</v>
       </c>
       <c r="I37" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>3.85</v>
@@ -9789,22 +9789,22 @@
         <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U37" t="n">
         <v>2.62</v>
       </c>
       <c r="V37" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W37" t="n">
         <v>1.38</v>
       </c>
       <c r="X37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y37" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Z37" t="n">
         <v>19.5</v>
@@ -9816,7 +9816,7 @@
         <v>22</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD37" t="n">
         <v>13.5</v>
@@ -9825,19 +9825,19 @@
         <v>25</v>
       </c>
       <c r="AF37" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AG37" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
         <v>20</v>
       </c>
       <c r="AI37" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AJ37" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="n">
         <v>44</v>
@@ -9849,25 +9849,25 @@
         <v>85</v>
       </c>
       <c r="AN37" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AO37" t="n">
         <v>14</v>
       </c>
       <c r="AP37" t="n">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="AQ37" t="n">
         <v>11.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS37" t="n">
         <v>19</v>
       </c>
       <c r="AT37" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AU37" t="n">
         <v>8.4</v>
@@ -9876,31 +9876,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX37" t="n">
         <v>20</v>
       </c>
       <c r="AY37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ37" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BA37" t="n">
         <v>20</v>
       </c>
       <c r="BB37" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF37" t="n">
         <v>18.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -10004,13 +10004,13 @@
         <v>1.76</v>
       </c>
       <c r="G38" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H38" t="n">
         <v>4.8</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -10040,7 +10040,7 @@
         <v>1.51</v>
       </c>
       <c r="S38" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T38" t="n">
         <v>1.73</v>
@@ -10052,7 +10052,7 @@
         <v>1.24</v>
       </c>
       <c r="W38" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X38" t="n">
         <v>21</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
         <v>1.03</v>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O39" t="n">
         <v>1.21</v>
@@ -10288,7 +10288,7 @@
         <v>2.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R39" t="n">
         <v>1.58</v>
@@ -10297,7 +10297,7 @@
         <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U39" t="n">
         <v>1.89</v>
@@ -10345,7 +10345,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK39" t="n">
         <v>14</v>
@@ -10357,16 +10357,16 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ39" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AR39" t="n">
         <v>38</v>
@@ -10375,13 +10375,13 @@
         <v>95</v>
       </c>
       <c r="AT39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV39" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AW39" t="n">
         <v>44</v>
@@ -10390,10 +10390,10 @@
         <v>7.4</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA39" t="n">
         <v>42</v>
@@ -10411,7 +10411,7 @@
         <v>44</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG39" t="n">
         <v>48</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -10515,16 +10515,16 @@
         <v>1.5</v>
       </c>
       <c r="H40" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I40" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K40" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L40" t="n">
         <v>1.26</v>
@@ -10536,34 +10536,34 @@
         <v>4.8</v>
       </c>
       <c r="O40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P40" t="n">
         <v>2.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R40" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T40" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U40" t="n">
         <v>1.96</v>
       </c>
       <c r="V40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W40" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X40" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y40" t="n">
         <v>36</v>
@@ -10572,22 +10572,22 @@
         <v>85</v>
       </c>
       <c r="AA40" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB40" t="n">
         <v>11.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD40" t="n">
         <v>32</v>
       </c>
       <c r="AE40" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG40" t="n">
         <v>12</v>
@@ -10608,7 +10608,7 @@
         <v>38</v>
       </c>
       <c r="AM40" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN40" t="n">
         <v>6.6</v>
@@ -10617,58 +10617,58 @@
         <v>150</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX40" t="n">
         <v>3.7</v>
       </c>
-      <c r="AU40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV40" t="n">
+      <c r="AY40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF40" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>2.98</v>
-      </c>
       <c r="BG40" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
         <v>1.96</v>
       </c>
       <c r="H41" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
         <v>4.1</v>
@@ -10778,7 +10778,7 @@
         <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.24</v>
@@ -10787,13 +10787,13 @@
         <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O41" t="n">
         <v>1.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q41" t="n">
         <v>1.58</v>
@@ -10808,7 +10808,7 @@
         <v>1.56</v>
       </c>
       <c r="U41" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V41" t="n">
         <v>1.32</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -11017,22 +11017,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11041,34 +11041,34 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="O42" t="n">
         <v>1.11</v>
       </c>
       <c r="P42" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T42" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.18</v>
-      </c>
       <c r="U42" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -11277,13 +11277,13 @@
         <v>1.8</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K43" t="n">
         <v>5.1</v>
@@ -11295,31 +11295,31 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O43" t="n">
         <v>1.15</v>
       </c>
       <c r="P43" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q43" t="n">
         <v>1.46</v>
       </c>
       <c r="R43" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S43" t="n">
         <v>2.14</v>
       </c>
       <c r="T43" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U43" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
         <v>2.24</v>
@@ -11349,7 +11349,7 @@
         <v>60</v>
       </c>
       <c r="AF43" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AG43" t="n">
         <v>13</v>
@@ -11364,7 +11364,7 @@
         <v>23</v>
       </c>
       <c r="AK43" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL43" t="n">
         <v>30</v>
@@ -11376,61 +11376,61 @@
         <v>7.6</v>
       </c>
       <c r="AO43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP43" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG43" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH43" t="n">
         <v>5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="G44" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H44" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="I44" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="J44" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K44" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="L44" t="n">
         <v>1.24</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.18</v>
       </c>
       <c r="P44" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q44" t="n">
         <v>1.53</v>
       </c>
       <c r="R44" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S44" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="T44" t="n">
         <v>2.14</v>
@@ -11573,7 +11573,7 @@
         <v>1.74</v>
       </c>
       <c r="V44" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W44" t="n">
         <v>1.05</v>
@@ -11594,7 +11594,7 @@
         <v>60</v>
       </c>
       <c r="AC44" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD44" t="n">
         <v>13.5</v>
@@ -11606,10 +11606,10 @@
         <v>180</v>
       </c>
       <c r="AG44" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AH44" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AI44" t="n">
         <v>48</v>
@@ -11618,73 +11618,73 @@
         <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AL44" t="n">
         <v>220</v>
       </c>
       <c r="AM44" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN44" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AO44" t="n">
         <v>4.2</v>
       </c>
       <c r="AP44" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AQ44" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AR44" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="AV44" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY44" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB44" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG44" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="BH44" t="n">
         <v>4.6</v>
@@ -11738,7 +11738,7 @@
         <v>23</v>
       </c>
       <c r="BY44" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ44" t="n">
         <v>9.6</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -11806,19 +11806,19 @@
         <v>1.09</v>
       </c>
       <c r="O45" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R45" t="n">
         <v>1.08</v>
       </c>
       <c r="S45" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>1.56</v>
       </c>
       <c r="G46" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H46" t="n">
         <v>5.7</v>
@@ -12045,7 +12045,7 @@
         <v>7.8</v>
       </c>
       <c r="J46" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K46" t="n">
         <v>5.4</v>
@@ -12057,34 +12057,34 @@
         <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.24</v>
       </c>
       <c r="P46" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S46" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="T46" t="n">
         <v>1.8</v>
       </c>
       <c r="U46" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V46" t="n">
         <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X46" t="n">
         <v>23</v>
@@ -12141,79 +12141,79 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AR46" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="AS46" t="n">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AW46" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="AX46" t="n">
-        <v>2.68</v>
+        <v>8</v>
       </c>
       <c r="AY46" t="n">
-        <v>2.74</v>
+        <v>3.95</v>
       </c>
       <c r="AZ46" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BA46" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="BB46" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="BC46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI46" t="n">
         <v>2.96</v>
       </c>
-      <c r="BD46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BJ46" t="n">
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="BN46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO46" t="n">
         <v>3.5</v>
@@ -12228,7 +12228,7 @@
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
@@ -12240,13 +12240,13 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY46" t="n">
         <v>1.59</v>
-      </c>
-      <c r="BX46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY46" t="n">
-        <v>1.06</v>
       </c>
       <c r="BZ46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G47" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L47" t="n">
         <v>1.44</v>
@@ -12317,7 +12317,7 @@
         <v>1.46</v>
       </c>
       <c r="P47" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q47" t="n">
         <v>2.16</v>
@@ -12332,13 +12332,13 @@
         <v>2.08</v>
       </c>
       <c r="U47" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V47" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W47" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X47" t="n">
         <v>12</v>
@@ -12353,7 +12353,7 @@
         <v>180</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC47" t="n">
         <v>9.4</v>
@@ -12365,7 +12365,7 @@
         <v>110</v>
       </c>
       <c r="AF47" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG47" t="n">
         <v>13</v>
@@ -12377,7 +12377,7 @@
         <v>120</v>
       </c>
       <c r="AJ47" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK47" t="n">
         <v>30</v>
@@ -12395,70 +12395,70 @@
         <v>170</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW47" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW47" t="n">
+      <c r="AX47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD47" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ47" t="n">
+      <c r="BE47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF47" t="n">
         <v>3.9</v>
       </c>
-      <c r="BA47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG47" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI47" t="n">
         <v>2.46</v>
       </c>
       <c r="BJ47" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
@@ -12470,47 +12470,47 @@
         <v>4.5</v>
       </c>
       <c r="BO47" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP47" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ47" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS47" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BT47" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU47" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV47" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY47" t="n">
         <v>2.22</v>
       </c>
-      <c r="BX47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY47" t="n">
-        <v>2.24</v>
-      </c>
       <c r="BZ47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA47" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
         <v>1.11</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -12565,22 +12565,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O48" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="R48" t="n">
         <v>1.08</v>
       </c>
       <c r="S48" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
         <v>4.1</v>
       </c>
       <c r="O50" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P50" t="n">
         <v>2.06</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G51" t="n">
         <v>2.66</v>
       </c>
       <c r="H51" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I51" t="n">
         <v>3.75</v>
@@ -13318,10 +13318,10 @@
         <v>3.1</v>
       </c>
       <c r="K51" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L51" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M51" t="n">
         <v>1.1</v>
@@ -13333,7 +13333,7 @@
         <v>1.43</v>
       </c>
       <c r="P51" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q51" t="n">
         <v>2.24</v>
@@ -13342,16 +13342,16 @@
         <v>1.24</v>
       </c>
       <c r="S51" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T51" t="n">
         <v>1.89</v>
       </c>
       <c r="U51" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V51" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
         <v>1.6</v>
@@ -13360,7 +13360,7 @@
         <v>12.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z51" t="n">
         <v>27</v>
@@ -13369,13 +13369,13 @@
         <v>80</v>
       </c>
       <c r="AB51" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC51" t="n">
         <v>8.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE51" t="n">
         <v>55</v>
@@ -13402,16 +13402,16 @@
         <v>60</v>
       </c>
       <c r="AM51" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN51" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO51" t="n">
         <v>65</v>
       </c>
       <c r="AP51" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ51" t="n">
         <v>8.4</v>
@@ -13420,19 +13420,19 @@
         <v>17.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT51" t="n">
         <v>7.4</v>
       </c>
       <c r="AU51" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX51" t="n">
         <v>11.5</v>
@@ -13441,34 +13441,34 @@
         <v>9.4</v>
       </c>
       <c r="AZ51" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC51" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD51" t="n">
-        <v>4.6</v>
+        <v>36</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH51" t="n">
         <v>3.1</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ51" t="n">
         <v>11</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -13587,13 +13587,13 @@
         <v>1.37</v>
       </c>
       <c r="P52" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R52" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S52" t="n">
         <v>3.85</v>
@@ -13614,7 +13614,7 @@
         <v>14.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z52" t="n">
         <v>40</v>
@@ -13635,7 +13635,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG52" t="n">
         <v>12</v>
@@ -13644,25 +13644,25 @@
         <v>24</v>
       </c>
       <c r="AI52" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK52" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL52" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM52" t="n">
         <v>150</v>
       </c>
       <c r="AN52" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="n">
         <v>10.5</v>
@@ -13671,10 +13671,10 @@
         <v>12.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS52" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT52" t="n">
         <v>6.8</v>
@@ -13686,7 +13686,7 @@
         <v>15.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX52" t="n">
         <v>9.800000000000001</v>
@@ -13698,7 +13698,7 @@
         <v>17.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB52" t="n">
         <v>19.5</v>
@@ -13707,16 +13707,16 @@
         <v>19</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF52" t="n">
         <v>12.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH52" t="n">
         <v>3.35</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
         <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T53" t="n">
         <v>1.98</v>
@@ -13868,7 +13868,7 @@
         <v>12.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z53" t="n">
         <v>30</v>
@@ -13895,10 +13895,10 @@
         <v>11.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI53" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ53" t="n">
         <v>29</v>
@@ -13925,10 +13925,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR53" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT53" t="n">
         <v>7</v>
@@ -13940,7 +13940,7 @@
         <v>13.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX53" t="n">
         <v>10</v>
@@ -13952,7 +13952,7 @@
         <v>18.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB53" t="n">
         <v>21</v>
@@ -13964,16 +13964,16 @@
         <v>40</v>
       </c>
       <c r="BE53" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF53" t="n">
         <v>18</v>
       </c>
       <c r="BG53" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH53" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI53" t="n">
         <v>2.52</v>
@@ -13982,13 +13982,13 @@
         <v>11</v>
       </c>
       <c r="BK53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN53" t="n">
         <v>4.7</v>
@@ -14000,13 +14000,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ53" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR53" t="n">
         <v>36</v>
       </c>
       <c r="BS53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT53" t="n">
         <v>7.4</v>
@@ -14018,23 +14018,23 @@
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ53" t="n">
         <v>36</v>
       </c>
       <c r="CA53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
         <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R54" t="n">
         <v>1.29</v>
@@ -14140,7 +14140,7 @@
         <v>12.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF54" t="n">
         <v>19.5</v>
@@ -14182,7 +14182,7 @@
         <v>16</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT54" t="n">
         <v>9.6</v>
@@ -14203,13 +14203,13 @@
         <v>11</v>
       </c>
       <c r="AZ54" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB54" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC54" t="n">
         <v>5.1</v>
@@ -14218,7 +14218,7 @@
         <v>5.5</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF54" t="n">
         <v>5.1</v>
@@ -14230,10 +14230,10 @@
         <v>3.15</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ54" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK54" t="n">
         <v>6</v>
@@ -14254,13 +14254,13 @@
         <v>23</v>
       </c>
       <c r="BQ54" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT54" t="n">
         <v>5.8</v>
@@ -14272,23 +14272,23 @@
         <v>23</v>
       </c>
       <c r="BW54" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ54" t="n">
         <v>34</v>
       </c>
       <c r="CA54" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -14573,58 +14573,58 @@
         </is>
       </c>
       <c r="F56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K56" t="n">
         <v>4.3</v>
       </c>
-      <c r="G56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L56" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M56" t="n">
         <v>1.05</v>
       </c>
       <c r="N56" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O56" t="n">
         <v>1.26</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R56" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S56" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="T56" t="n">
         <v>1.74</v>
       </c>
       <c r="U56" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V56" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W56" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X56" t="n">
         <v>21</v>
@@ -14642,64 +14642,64 @@
         <v>23</v>
       </c>
       <c r="AC56" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD56" t="n">
         <v>12.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF56" t="n">
         <v>48</v>
       </c>
       <c r="AG56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH56" t="n">
         <v>23</v>
       </c>
       <c r="AI56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ56" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK56" t="n">
         <v>75</v>
       </c>
       <c r="AL56" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM56" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN56" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO56" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP56" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR56" t="n">
         <v>1.03</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW56" t="n">
         <v>1.03</v>
@@ -14708,10 +14708,10 @@
         <v>1.03</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA56" t="n">
         <v>1.03</v>
@@ -14732,19 +14732,19 @@
         <v>1.01</v>
       </c>
       <c r="BG56" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH56" t="n">
         <v>3.9</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="BJ56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK56" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
@@ -14753,7 +14753,7 @@
         <v>1.01</v>
       </c>
       <c r="BN56" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO56" t="n">
         <v>6.2</v>
@@ -14765,10 +14765,10 @@
         <v>27</v>
       </c>
       <c r="BR56" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT56" t="n">
         <v>4.8</v>
@@ -14789,14 +14789,14 @@
         <v>17.5</v>
       </c>
       <c r="BZ56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA56" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
         <v>1000</v>
       </c>
       <c r="J57" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K57" t="n">
         <v>1000</v>
@@ -14851,22 +14851,22 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="O57" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P57" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R57" t="n">
         <v>1.05</v>
       </c>
       <c r="S57" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -14935,52 +14935,52 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF57" t="n">
         <v>1.01</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
         <v>1000</v>
       </c>
       <c r="J58" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K58" t="n">
         <v>1000</v>
@@ -15105,22 +15105,22 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="O58" t="n">
         <v>1.01</v>
       </c>
       <c r="P58" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R58" t="n">
         <v>1.05</v>
       </c>
       <c r="S58" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="T58" t="n">
         <v>1.01</v>
@@ -15189,52 +15189,52 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -15341,46 +15341,46 @@
         <v>2.4</v>
       </c>
       <c r="H59" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I59" t="n">
         <v>4.8</v>
       </c>
       <c r="J59" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K59" t="n">
         <v>3.15</v>
       </c>
       <c r="L59" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M59" t="n">
         <v>1.15</v>
       </c>
       <c r="N59" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O59" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="P59" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="R59" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S59" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="T59" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U59" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V59" t="n">
         <v>1.27</v>
@@ -15389,7 +15389,7 @@
         <v>1.71</v>
       </c>
       <c r="X59" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y59" t="n">
         <v>12.5</v>
@@ -15401,7 +15401,7 @@
         <v>150</v>
       </c>
       <c r="AB59" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC59" t="n">
         <v>8.800000000000001</v>
@@ -15443,112 +15443,112 @@
         <v>200</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AQ59" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AU59" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AV59" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX59" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AY59" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB59" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BC59" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF59" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG59" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH59" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BJ59" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK59" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BN59" t="n">
         <v>4.9</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP59" t="n">
         <v>22</v>
       </c>
       <c r="BQ59" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR59" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS59" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT59" t="n">
         <v>7.8</v>
       </c>
       <c r="BU59" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV59" t="n">
         <v>55</v>
       </c>
       <c r="BW59" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY59" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BX59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY59" t="n">
-        <v>7.2</v>
       </c>
       <c r="BZ59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
         <v>1000</v>
       </c>
       <c r="J60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K60" t="n">
         <v>1000</v>
@@ -15613,22 +15613,22 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="O60" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P60" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R60" t="n">
         <v>1.05</v>
       </c>
       <c r="S60" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T60" t="n">
         <v>1.01</v>
@@ -15697,52 +15697,52 @@
         <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF60" t="n">
         <v>1.01</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
         <v>3.55</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J61" t="n">
         <v>3.05</v>
@@ -16008,7 +16008,7 @@
         <v>1000</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -16097,127 +16097,127 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="G62" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="H62" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J62" t="n">
         <v>3.25</v>
       </c>
       <c r="K62" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L62" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M62" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N62" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O62" t="n">
         <v>1.31</v>
       </c>
       <c r="P62" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
         <v>1.83</v>
       </c>
       <c r="R62" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T62" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U62" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W62" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="X62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y62" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA62" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AB62" t="n">
         <v>10.5</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE62" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG62" t="n">
         <v>12</v>
       </c>
       <c r="AH62" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ62" t="n">
         <v>22</v>
       </c>
-      <c r="AI62" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>27</v>
-      </c>
       <c r="AK62" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL62" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM62" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN62" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO62" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP62" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AQ62" t="n">
         <v>4</v>
       </c>
       <c r="AR62" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS62" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AU62" t="n">
         <v>3.35</v>
@@ -16226,43 +16226,43 @@
         <v>4.1</v>
       </c>
       <c r="AW62" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX62" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AY62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF62" t="n">
         <v>3.6</v>
       </c>
-      <c r="AZ62" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG62" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH62" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI62" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ62" t="n">
         <v>10.5</v>
@@ -16274,43 +16274,43 @@
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BN62" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO62" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BP62" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BQ62" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BR62" t="n">
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT62" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU62" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BZ62" t="n">
         <v>0</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K64" t="n">
         <v>4.7</v>
@@ -16638,13 +16638,13 @@
         <v>1.98</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R64" t="n">
         <v>1.37</v>
       </c>
       <c r="S64" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T64" t="n">
         <v>1.91</v>
@@ -16653,7 +16653,7 @@
         <v>1.9</v>
       </c>
       <c r="V64" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W64" t="n">
         <v>2.48</v>
@@ -16770,7 +16770,7 @@
         <v>3.8</v>
       </c>
       <c r="BI64" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ64" t="n">
         <v>11</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -16859,10 +16859,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G65" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H65" t="n">
         <v>3.85</v>
@@ -16874,7 +16874,7 @@
         <v>3.05</v>
       </c>
       <c r="K65" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L65" t="n">
         <v>1.46</v>
@@ -16907,10 +16907,10 @@
         <v>1.8</v>
       </c>
       <c r="V65" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W65" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X65" t="n">
         <v>11</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -17113,70 +17113,70 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G66" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H66" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K66" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L66" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M66" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P66" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="R66" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S66" t="n">
         <v>3.45</v>
       </c>
       <c r="T66" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="U66" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="V66" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W66" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="X66" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y66" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z66" t="n">
         <v>36</v>
       </c>
       <c r="AA66" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB66" t="n">
         <v>9.4</v>
@@ -17185,49 +17185,49 @@
         <v>9</v>
       </c>
       <c r="AD66" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE66" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF66" t="n">
         <v>13</v>
       </c>
       <c r="AG66" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI66" t="n">
         <v>85</v>
       </c>
       <c r="AJ66" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AK66" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL66" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM66" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN66" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AO66" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AP66" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS66" t="n">
         <v>1.03</v>
@@ -17248,10 +17248,10 @@
         <v>1.03</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA66" t="n">
         <v>1.03</v>
@@ -17263,28 +17263,28 @@
         <v>1.03</v>
       </c>
       <c r="BD66" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BE66" t="n">
         <v>1.03</v>
       </c>
       <c r="BF66" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG66" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BH66" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BI66" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BJ66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK66" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL66" t="n">
         <v>1000</v>
@@ -17293,50 +17293,50 @@
         <v>1.01</v>
       </c>
       <c r="BN66" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO66" t="n">
         <v>3.8</v>
       </c>
       <c r="BP66" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BQ66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BR66" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS66" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BT66" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU66" t="n">
         <v>5.8</v>
       </c>
       <c r="BV66" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BW66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BX66" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY66" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ66" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="CA66" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17370,7 @@
         <v>2.44</v>
       </c>
       <c r="G67" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H67" t="n">
         <v>3</v>
@@ -17391,13 +17391,13 @@
         <v>1.09</v>
       </c>
       <c r="N67" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="O67" t="n">
         <v>1.41</v>
       </c>
       <c r="P67" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Q67" t="n">
         <v>2.04</v>
@@ -17406,7 +17406,7 @@
         <v>1.25</v>
       </c>
       <c r="S67" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T67" t="n">
         <v>1.87</v>
@@ -17415,7 +17415,7 @@
         <v>1.94</v>
       </c>
       <c r="V67" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W67" t="n">
         <v>1.58</v>
@@ -17532,7 +17532,7 @@
         <v>3.1</v>
       </c>
       <c r="BI67" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="BJ67" t="n">
         <v>10.5</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -17621,10 +17621,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G68" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H68" t="n">
         <v>6.4</v>
@@ -17639,43 +17639,43 @@
         <v>4.8</v>
       </c>
       <c r="L68" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M68" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N68" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O68" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P68" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R68" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S68" t="n">
         <v>3.2</v>
       </c>
       <c r="T68" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U68" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V68" t="n">
         <v>1.11</v>
       </c>
       <c r="W68" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X68" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y68" t="n">
         <v>26</v>
@@ -17684,10 +17684,10 @@
         <v>80</v>
       </c>
       <c r="AA68" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB68" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC68" t="n">
         <v>11.5</v>
@@ -17699,7 +17699,7 @@
         <v>160</v>
       </c>
       <c r="AF68" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG68" t="n">
         <v>12</v>
@@ -17717,76 +17717,76 @@
         <v>21</v>
       </c>
       <c r="AL68" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM68" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN68" t="n">
         <v>11</v>
       </c>
       <c r="AO68" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP68" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ68" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR68" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS68" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT68" t="n">
         <v>3.3</v>
       </c>
       <c r="AU68" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV68" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW68" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX68" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AY68" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF68" t="n">
         <v>3.75</v>
       </c>
-      <c r="AZ68" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BG68" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH68" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI68" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ68" t="n">
         <v>12</v>
@@ -17798,7 +17798,7 @@
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BN68" t="n">
         <v>4.1</v>
@@ -17828,23 +17828,23 @@
         <v>1000</v>
       </c>
       <c r="BW68" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BX68" t="n">
         <v>1000</v>
       </c>
       <c r="BY68" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BZ68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA68" t="n">
         <v>6.8</v>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -17875,13 +17875,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G69" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H69" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I69" t="n">
         <v>4.7</v>
@@ -17893,13 +17893,13 @@
         <v>3.45</v>
       </c>
       <c r="L69" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M69" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N69" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O69" t="n">
         <v>1.5</v>
@@ -17911,10 +17911,10 @@
         <v>2.44</v>
       </c>
       <c r="R69" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S69" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T69" t="n">
         <v>2.06</v>
@@ -17926,49 +17926,49 @@
         <v>1.27</v>
       </c>
       <c r="W69" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X69" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z69" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA69" t="n">
         <v>120</v>
       </c>
       <c r="AB69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC69" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC69" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD69" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE69" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF69" t="n">
         <v>13</v>
       </c>
       <c r="AG69" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH69" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI69" t="n">
         <v>110</v>
       </c>
       <c r="AJ69" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK69" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL69" t="n">
         <v>65</v>
@@ -17977,82 +17977,82 @@
         <v>210</v>
       </c>
       <c r="AN69" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO69" t="n">
         <v>120</v>
       </c>
       <c r="AP69" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ69" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AR69" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT69" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AU69" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AV69" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AW69" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX69" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX69" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AY69" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AZ69" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB69" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BC69" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BD69" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF69" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG69" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH69" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BI69" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ69" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK69" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
       </c>
       <c r="BM69" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BN69" t="n">
         <v>4.9</v>
@@ -18064,10 +18064,10 @@
         <v>19</v>
       </c>
       <c r="BQ69" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BR69" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS69" t="n">
         <v>2.16</v>
@@ -18082,13 +18082,13 @@
         <v>44</v>
       </c>
       <c r="BW69" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BX69" t="n">
         <v>65</v>
       </c>
       <c r="BY69" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ69" t="n">
         <v>0</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -18129,16 +18129,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G70" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H70" t="n">
         <v>7.2</v>
       </c>
       <c r="I70" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J70" t="n">
         <v>3.8</v>
@@ -18159,10 +18159,10 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-04.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -881,34 +881,34 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -917,25 +917,25 @@
         <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AB2" t="n">
         <v>8.4</v>
       </c>
       <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -944,13 +944,13 @@
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
@@ -959,64 +959,64 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AV2" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1126,16 +1126,16 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
         <v>1.41</v>
@@ -1153,16 +1153,16 @@
         <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1189,7 +1189,7 @@
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
@@ -1204,10 +1204,10 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1249,7 +1249,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
         <v>44</v>
@@ -1264,7 +1264,7 @@
         <v>29</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
         <v>1.58</v>
@@ -1407,16 +1407,16 @@
         <v>5.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
         <v>9.199999999999999</v>
@@ -1485,7 +1485,7 @@
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>6.6</v>
@@ -1506,7 +1506,7 @@
         <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1515,7 +1515,7 @@
         <v>36</v>
       </c>
       <c r="BD4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE4" t="n">
         <v>70</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
         <v>2.22</v>
@@ -1661,10 +1661,10 @@
         <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
         <v>1.21</v>
@@ -1676,22 +1676,22 @@
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB5" t="n">
         <v>7.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>480</v>
@@ -1703,19 +1703,19 @@
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
         <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1724,7 +1724,7 @@
         <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1736,7 +1736,7 @@
         <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>6.8</v>
@@ -1748,7 +1748,7 @@
         <v>19.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AX5" t="n">
         <v>8.800000000000001</v>
@@ -1760,19 +1760,19 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC5" t="n">
         <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
         <v>2.48</v>
@@ -1882,7 +1882,7 @@
         <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1900,10 +1900,10 @@
         <v>2.98</v>
       </c>
       <c r="O6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
         <v>2.48</v>
@@ -1921,13 +1921,13 @@
         <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
         <v>1.67</v>
       </c>
       <c r="X6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
@@ -1963,13 +1963,13 @@
         <v>150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AM6" t="n">
         <v>570</v>
@@ -2014,7 +2014,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -2151,7 +2151,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
@@ -2163,22 +2163,22 @@
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
         <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>24</v>
@@ -2187,16 +2187,16 @@
         <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB7" t="n">
         <v>28</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
         <v>12</v>
@@ -2208,10 +2208,10 @@
         <v>60</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
         <v>32</v>
@@ -2220,13 +2220,13 @@
         <v>180</v>
       </c>
       <c r="AK7" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
         <v>100</v>
@@ -2238,19 +2238,19 @@
         <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
         <v>9.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
         <v>19.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -2262,7 +2262,7 @@
         <v>34</v>
       </c>
       <c r="AY7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>17</v>
@@ -2277,10 +2277,10 @@
         <v>48</v>
       </c>
       <c r="BD7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF7" t="n">
         <v>44</v>
@@ -2307,7 +2307,7 @@
         <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BO7" t="n">
         <v>7.4</v>
@@ -2319,16 +2319,16 @@
         <v>11.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
         <v>12</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="n">
         <v>1.88</v>
@@ -2411,19 +2411,19 @@
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
         <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
         <v>2.06</v>
@@ -2441,10 +2441,10 @@
         <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB8" t="n">
         <v>20</v>
@@ -2453,7 +2453,7 @@
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8" t="n">
         <v>24</v>
@@ -2525,7 +2525,7 @@
         <v>27</v>
       </c>
       <c r="BB8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BC8" t="n">
         <v>40</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G9" t="n">
         <v>2.06</v>
@@ -2647,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
@@ -2656,25 +2656,25 @@
         <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
         <v>2.34</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
         <v>2.04</v>
@@ -2710,13 +2710,13 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
         <v>11.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2725,10 +2725,10 @@
         <v>130</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>50</v>
@@ -2737,7 +2737,7 @@
         <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>600</v>
@@ -2755,7 +2755,7 @@
         <v>75</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
@@ -2770,7 +2770,7 @@
         <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>3.25</v>
@@ -2898,10 +2898,10 @@
         <v>2.42</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>3.65</v>
@@ -2916,13 +2916,13 @@
         <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -2943,55 +2943,55 @@
         <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>16.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="n">
         <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AO10" t="n">
         <v>28</v>
@@ -3027,7 +3027,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -3039,16 +3039,16 @@
         <v>25</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BF10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -3176,16 +3176,16 @@
         <v>2.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
         <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U11" t="n">
         <v>2.68</v>
@@ -3212,7 +3212,7 @@
         <v>17.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
@@ -3221,7 +3221,7 @@
         <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG11" t="n">
         <v>14</v>
@@ -3266,7 +3266,7 @@
         <v>15</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
@@ -3287,19 +3287,19 @@
         <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BC11" t="n">
         <v>23</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE11" t="n">
         <v>40</v>
       </c>
       <c r="BF11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
         <v>11.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3400,22 +3400,22 @@
         <v>1.87</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -3424,7 +3424,7 @@
         <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
         <v>1.61</v>
@@ -3439,16 +3439,16 @@
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
         <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -3505,7 +3505,7 @@
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>11</v>
@@ -3535,13 +3535,13 @@
         <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
         <v>7.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
         <v>21</v>
@@ -3553,16 +3553,16 @@
         <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>18.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
         <v>7.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
         <v>12.5</v>
@@ -3574,19 +3574,19 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN12" t="n">
         <v>4.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP12" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
         <v>5.8</v>
@@ -3666,58 +3666,58 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M13" t="n">
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O13" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>130</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>660</v>
+        <v>40</v>
       </c>
       <c r="AC13" t="n">
         <v>42</v>
@@ -3729,10 +3729,10 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>130</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
         <v>130</v>
@@ -3759,122 +3759,122 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.66</v>
+        <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>9</v>
+        <v>1.06</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>12.5</v>
+        <v>1.06</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.9</v>
+        <v>1.41</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3935,7 +3935,7 @@
         <v>1.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
         <v>2.12</v>
@@ -3947,16 +3947,16 @@
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
         <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -3965,7 +3965,7 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
         <v>90</v>
@@ -3977,10 +3977,10 @@
         <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
         <v>16.5</v>
@@ -4022,7 +4022,7 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8</v>
@@ -4049,16 +4049,16 @@
         <v>22</v>
       </c>
       <c r="BB14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD14" t="n">
         <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
         <v>18</v>
@@ -4088,7 +4088,7 @@
         <v>4.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP14" t="n">
         <v>16.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4159,31 +4159,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.49</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
         <v>1.44</v>
@@ -4204,13 +4204,13 @@
         <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
@@ -4225,13 +4225,13 @@
         <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="AE15" t="n">
         <v>240</v>
@@ -4273,52 +4273,52 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>6.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="n">
         <v>3.05</v>
@@ -4330,31 +4330,31 @@
         <v>970</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO15" t="n">
         <v>3.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BT15" t="n">
         <v>8.6</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4437,28 +4437,28 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>1.31</v>
@@ -4479,7 +4479,7 @@
         <v>110</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -4488,7 +4488,7 @@
         <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
         <v>13.5</v>
@@ -4497,7 +4497,7 @@
         <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI16" t="n">
         <v>370</v>
@@ -4506,7 +4506,7 @@
         <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
@@ -4527,7 +4527,7 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>7.4</v>
@@ -4539,7 +4539,7 @@
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
         <v>34</v>
@@ -4548,25 +4548,25 @@
         <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BE16" t="n">
-        <v>44</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
@@ -4596,7 +4596,7 @@
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP16" t="n">
         <v>17</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G17" t="n">
         <v>2.74</v>
       </c>
       <c r="H17" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I17" t="n">
         <v>3.25</v>
@@ -4682,7 +4682,7 @@
         <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>1.44</v>
@@ -4706,7 +4706,7 @@
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
         <v>1.8</v>
@@ -4715,7 +4715,7 @@
         <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
         <v>1.58</v>
@@ -4748,7 +4748,7 @@
         <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>34</v>
@@ -4796,10 +4796,10 @@
         <v>8.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY17" t="n">
         <v>7</v>
@@ -4811,22 +4811,22 @@
         <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC17" t="n">
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
         <v>5.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="n">
         <v>3.25</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="G18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H18" t="n">
         <v>1.48</v>
       </c>
       <c r="I18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
@@ -4945,31 +4945,31 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
         <v>1.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
         <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
@@ -4987,7 +4987,7 @@
         <v>14.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AC18" t="n">
         <v>10.5</v>
@@ -5005,7 +5005,7 @@
         <v>34</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
         <v>50</v>
@@ -5020,7 +5020,7 @@
         <v>470</v>
       </c>
       <c r="AM18" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>270</v>
@@ -5032,7 +5032,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AR18" t="n">
         <v>7.2</v>
@@ -5047,43 +5047,43 @@
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW18" t="n">
         <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ18" t="n">
         <v>6.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD18" t="n">
         <v>8</v>
       </c>
-      <c r="BC18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI18" t="n">
         <v>3.05</v>
@@ -5092,34 +5092,34 @@
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.68</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
         <v>12</v>
       </c>
       <c r="BO18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>2.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BU18" t="n">
         <v>3.4</v>
@@ -5128,23 +5128,23 @@
         <v>10</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BX18" t="n">
         <v>29</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ18" t="n">
         <v>20</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5175,31 +5175,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H19" t="n">
         <v>2.14</v>
       </c>
       <c r="I19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
         <v>1.43</v>
@@ -5208,13 +5208,13 @@
         <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R19" t="n">
         <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
         <v>1.96</v>
@@ -5223,10 +5223,10 @@
         <v>1.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -5283,52 +5283,52 @@
         <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AS19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3</v>
       </c>
       <c r="BA19" t="n">
         <v>9.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="BF19" t="n">
         <v>9.199999999999999</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5432,10 +5432,10 @@
         <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
         <v>4.3</v>
@@ -5456,10 +5456,10 @@
         <v>2.52</v>
       </c>
       <c r="O20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
         <v>2.4</v>
@@ -5495,7 +5495,7 @@
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
@@ -5576,7 +5576,7 @@
         <v>6.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD20" t="n">
         <v>6.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>4.4</v>
@@ -5719,16 +5719,16 @@
         <v>1.41</v>
       </c>
       <c r="R21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>1.46</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V21" t="n">
         <v>1.28</v>
@@ -5767,7 +5767,7 @@
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
@@ -5788,19 +5788,19 @@
         <v>5.9</v>
       </c>
       <c r="AO21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
         <v>36</v>
       </c>
       <c r="AS21" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AT21" t="n">
         <v>15.5</v>
@@ -5815,25 +5815,25 @@
         <v>32</v>
       </c>
       <c r="AX21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC21" t="n">
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE21" t="n">
         <v>34</v>
@@ -5842,7 +5842,7 @@
         <v>5.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH21" t="n">
         <v>5.6</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
         <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
         <v>1.76</v>
@@ -5994,7 +5994,7 @@
         <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z22" t="n">
         <v>90</v>
@@ -6051,13 +6051,13 @@
         <v>18</v>
       </c>
       <c r="AR22" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AS22" t="n">
         <v>40</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
         <v>8.4</v>
@@ -6078,7 +6078,7 @@
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BB22" t="n">
         <v>16</v>
@@ -6096,7 +6096,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BH22" t="n">
         <v>3.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
         <v>32</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>29</v>
@@ -6320,7 +6320,7 @@
         <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX23" t="n">
         <v>14.5</v>
@@ -6341,7 +6341,7 @@
         <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
         <v>40</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>3.15</v>
       </c>
       <c r="G24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H24" t="n">
         <v>2.22</v>
@@ -6463,7 +6463,7 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -6493,7 +6493,7 @@
         <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W24" t="n">
         <v>1.37</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
         <v>50</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
         <v>8</v>
@@ -6780,7 +6780,7 @@
         <v>18</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
         <v>16</v>
@@ -6798,10 +6798,10 @@
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
         <v>27</v>
@@ -6813,10 +6813,10 @@
         <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AT25" t="n">
         <v>11</v>
@@ -6828,7 +6828,7 @@
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX25" t="n">
         <v>15.5</v>
@@ -6849,7 +6849,7 @@
         <v>22</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
         <v>55</v>
@@ -6858,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="BG25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BH25" t="n">
         <v>3.65</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7088,10 +7088,10 @@
         <v>5.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA26" t="n">
         <v>7.4</v>
@@ -7106,13 +7106,13 @@
         <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BF26" t="n">
         <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="n">
         <v>3.9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7207,64 +7207,64 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
         <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
         <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z27" t="n">
         <v>29</v>
@@ -7273,13 +7273,13 @@
         <v>170</v>
       </c>
       <c r="AB27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>95</v>
@@ -7288,19 +7288,19 @@
         <v>14.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ27" t="n">
         <v>44</v>
       </c>
       <c r="AK27" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
         <v>85</v>
@@ -7309,28 +7309,28 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO27" t="n">
         <v>44</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
         <v>13</v>
@@ -7342,16 +7342,16 @@
         <v>12.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>19.5</v>
+        <v>42</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
         <v>18</v>
@@ -7369,10 +7369,10 @@
         <v>27</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.6</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN27" t="n">
         <v>5.1</v>
@@ -7396,7 +7396,7 @@
         <v>16.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
@@ -7411,10 +7411,10 @@
         <v>6</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G28" t="n">
         <v>3.5</v>
@@ -7473,40 +7473,40 @@
         <v>2.42</v>
       </c>
       <c r="J28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R28" t="n">
         <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V28" t="n">
         <v>1.7</v>
@@ -7536,7 +7536,7 @@
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AF28" t="n">
         <v>24</v>
@@ -7563,16 +7563,16 @@
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO28" t="n">
         <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
         <v>12</v>
@@ -7587,25 +7587,25 @@
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX28" t="n">
         <v>16</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC28" t="n">
         <v>6.6</v>
@@ -7617,19 +7617,19 @@
         <v>7.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK28" t="n">
         <v>4.5</v>
@@ -7638,13 +7638,13 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.28</v>
+        <v>6.2</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
@@ -7656,10 +7656,10 @@
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU28" t="n">
         <v>4.1</v>
@@ -7668,13 +7668,13 @@
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H29" t="n">
         <v>2.16</v>
@@ -7727,13 +7727,13 @@
         <v>2.42</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7763,10 +7763,10 @@
         <v>2.24</v>
       </c>
       <c r="V29" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
         <v>970</v>
@@ -7784,7 +7784,7 @@
         <v>970</v>
       </c>
       <c r="AC29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD29" t="n">
         <v>970</v>
@@ -7817,7 +7817,7 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AO29" t="n">
         <v>85</v>
@@ -7829,10 +7829,10 @@
         <v>6.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT29" t="n">
         <v>8.4</v>
@@ -7847,7 +7847,7 @@
         <v>6.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY29" t="n">
         <v>8.4</v>
@@ -7856,13 +7856,13 @@
         <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BB29" t="n">
         <v>3.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BD29" t="n">
         <v>3.05</v>
@@ -7874,7 +7874,7 @@
         <v>6.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G30" t="n">
         <v>2.62</v>
@@ -7987,7 +7987,7 @@
         <v>3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -7999,13 +7999,13 @@
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
         <v>1.99</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
         <v>3.55</v>
@@ -8038,7 +8038,7 @@
         <v>12</v>
       </c>
       <c r="AC30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>16</v>
@@ -8050,16 +8050,16 @@
         <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
         <v>19.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK30" t="n">
         <v>36</v>
@@ -8071,40 +8071,40 @@
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>42</v>
       </c>
       <c r="AP30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AR30" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AX30" t="n">
         <v>12.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
         <v>13</v>
@@ -8113,7 +8113,7 @@
         <v>36</v>
       </c>
       <c r="BB30" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
@@ -8122,7 +8122,7 @@
         <v>30</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="BF30" t="n">
         <v>17.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8229,10 +8229,10 @@
         <v>3.7</v>
       </c>
       <c r="H31" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I31" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J31" t="n">
         <v>3.6</v>
@@ -8247,7 +8247,7 @@
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.29</v>
@@ -8268,7 +8268,7 @@
         <v>1.71</v>
       </c>
       <c r="U31" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V31" t="n">
         <v>1.8</v>
@@ -8286,10 +8286,10 @@
         <v>14.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC31" t="n">
         <v>8</v>
@@ -8301,10 +8301,10 @@
         <v>22</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>16</v>
@@ -8328,7 +8328,7 @@
         <v>36</v>
       </c>
       <c r="AO31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP31" t="n">
         <v>14.5</v>
@@ -8349,10 +8349,10 @@
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
@@ -8382,10 +8382,10 @@
         <v>29</v>
       </c>
       <c r="BG31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI31" t="n">
         <v>3.25</v>
@@ -8394,13 +8394,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN31" t="n">
         <v>6.8</v>
@@ -8418,7 +8418,7 @@
         <v>36</v>
       </c>
       <c r="BS31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT31" t="n">
         <v>5.2</v>
@@ -8430,23 +8430,23 @@
         <v>16</v>
       </c>
       <c r="BW31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX31" t="n">
         <v>28</v>
       </c>
       <c r="BY31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ31" t="n">
         <v>23</v>
       </c>
       <c r="CA31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8477,31 +8477,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I32" t="n">
         <v>2.5</v>
       </c>
-      <c r="I32" t="n">
-        <v>2.56</v>
-      </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
         <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.3</v>
@@ -8510,13 +8510,13 @@
         <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
         <v>1.74</v>
@@ -8525,13 +8525,13 @@
         <v>2.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X32" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y32" t="n">
         <v>12</v>
@@ -8540,7 +8540,7 @@
         <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB32" t="n">
         <v>13.5</v>
@@ -8549,22 +8549,22 @@
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF32" t="n">
         <v>23</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH32" t="n">
         <v>17.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ32" t="n">
         <v>55</v>
@@ -8582,25 +8582,25 @@
         <v>28</v>
       </c>
       <c r="AO32" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS32" t="n">
         <v>30</v>
       </c>
       <c r="AT32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
         <v>10.5</v>
@@ -8609,34 +8609,34 @@
         <v>22</v>
       </c>
       <c r="AX32" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ32" t="n">
         <v>14.5</v>
       </c>
       <c r="BA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC32" t="n">
         <v>29</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>24</v>
       </c>
       <c r="BD32" t="n">
         <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BF32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BG32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8734,13 +8734,13 @@
         <v>2.06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H33" t="n">
         <v>2.72</v>
       </c>
       <c r="I33" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8764,19 +8764,19 @@
         <v>3.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R33" t="n">
         <v>2.14</v>
       </c>
       <c r="S33" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="T33" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V33" t="n">
         <v>1.44</v>
@@ -8785,7 +8785,7 @@
         <v>1.83</v>
       </c>
       <c r="X33" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y33" t="n">
         <v>85</v>
@@ -8800,7 +8800,7 @@
         <v>75</v>
       </c>
       <c r="AC33" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AD33" t="n">
         <v>970</v>
@@ -8812,121 +8812,121 @@
         <v>75</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH33" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI33" t="n">
         <v>75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK33" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AM33" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AN33" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AO33" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.9</v>
+        <v>16</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.64</v>
+        <v>18</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.65</v>
+        <v>27</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.63</v>
+        <v>17.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.93</v>
+        <v>9.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.76</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.9</v>
+        <v>19</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.63</v>
+        <v>17</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.93</v>
+        <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.85</v>
+        <v>9.6</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.63</v>
+        <v>18</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.59</v>
+        <v>21</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.67</v>
+        <v>15.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.85</v>
+        <v>16.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ33" t="n">
         <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BN33" t="n">
         <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
@@ -8944,17 +8944,17 @@
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8985,97 +8985,97 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G34" t="n">
         <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="I34" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="J34" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R34" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S34" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="T34" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="U34" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V34" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
         <v>80</v>
       </c>
       <c r="Y34" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z34" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA34" t="n">
         <v>18</v>
       </c>
       <c r="AB34" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="AC34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD34" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE34" t="n">
         <v>15</v>
       </c>
       <c r="AF34" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="AG34" t="n">
         <v>30</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AK34" t="n">
         <v>400</v>
@@ -9093,58 +9093,58 @@
         <v>5.1</v>
       </c>
       <c r="AP34" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS34" t="n">
         <v>11.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW34" t="n">
         <v>10.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="AY34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ34" t="n">
         <v>14</v>
       </c>
       <c r="BA34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BD34" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BE34" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BF34" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH34" t="n">
         <v>5.4</v>
@@ -9153,28 +9153,28 @@
         <v>4.8</v>
       </c>
       <c r="BJ34" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BN34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ34" t="n">
         <v>11</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>11.5</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
@@ -9183,16 +9183,16 @@
         <v>11</v>
       </c>
       <c r="BT34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU34" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BV34" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BW34" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
@@ -9201,14 +9201,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CA34" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -9242,10 +9242,10 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I35" t="n">
         <v>3.3</v>
@@ -9254,163 +9254,163 @@
         <v>4.6</v>
       </c>
       <c r="K35" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U35" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V35" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W35" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X35" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="Y35" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="Z35" t="n">
         <v>140</v>
       </c>
       <c r="AA35" t="n">
-        <v>900</v>
+        <v>470</v>
       </c>
       <c r="AB35" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AC35" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AD35" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE35" t="n">
         <v>75</v>
       </c>
       <c r="AF35" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AG35" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="AI35" t="n">
         <v>60</v>
       </c>
       <c r="AJ35" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AK35" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AL35" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM35" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN35" t="n">
-        <v>55</v>
+        <v>7.6</v>
       </c>
       <c r="AO35" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.95</v>
+        <v>18.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.8</v>
+        <v>29</v>
       </c>
       <c r="AT35" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="AU35" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>15.5</v>
       </c>
       <c r="BE35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI35" t="n">
         <v>4</v>
       </c>
-      <c r="BF35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9428,7 +9428,7 @@
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
@@ -9440,7 +9440,7 @@
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -9496,22 +9496,22 @@
         <v>2.36</v>
       </c>
       <c r="G36" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H36" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I36" t="n">
         <v>2.74</v>
       </c>
       <c r="J36" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K36" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
@@ -9526,13 +9526,13 @@
         <v>3.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R36" t="n">
         <v>2.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="T36" t="n">
         <v>1.33</v>
@@ -9601,58 +9601,58 @@
         <v>10</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ36" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU36" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AV36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX36" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AY36" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA36" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BC36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BE36" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BF36" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH36" t="n">
         <v>6.6</v>
@@ -9670,25 +9670,25 @@
         <v>44</v>
       </c>
       <c r="BM36" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN36" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP36" t="n">
         <v>16</v>
       </c>
       <c r="BQ36" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR36" t="n">
         <v>18.5</v>
       </c>
       <c r="BS36" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT36" t="n">
         <v>7.2</v>
@@ -9697,16 +9697,16 @@
         <v>5.3</v>
       </c>
       <c r="BV36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX36" t="n">
         <v>18.5</v>
       </c>
       <c r="BY36" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -9750,10 +9750,10 @@
         <v>3.45</v>
       </c>
       <c r="G37" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H37" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I37" t="n">
         <v>2.18</v>
@@ -9765,7 +9765,7 @@
         <v>4.1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
@@ -9777,7 +9777,7 @@
         <v>1.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
         <v>1.62</v>
@@ -9807,7 +9807,7 @@
         <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="n">
         <v>27</v>
@@ -9819,16 +9819,16 @@
         <v>10</v>
       </c>
       <c r="AD37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF37" t="n">
         <v>48</v>
       </c>
       <c r="AG37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH37" t="n">
         <v>18</v>
@@ -9840,7 +9840,7 @@
         <v>120</v>
       </c>
       <c r="AK37" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AL37" t="n">
         <v>46</v>
@@ -9855,7 +9855,7 @@
         <v>12</v>
       </c>
       <c r="AP37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ37" t="n">
         <v>12.5</v>
@@ -9864,10 +9864,10 @@
         <v>14</v>
       </c>
       <c r="AS37" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU37" t="n">
         <v>8.4</v>
@@ -9888,10 +9888,10 @@
         <v>13.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC37" t="n">
         <v>21</v>
@@ -9918,13 +9918,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN37" t="n">
         <v>7.2</v>
@@ -9936,10 +9936,10 @@
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR37" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
         <v>10.5</v>
@@ -9948,7 +9948,7 @@
         <v>5.3</v>
       </c>
       <c r="BU37" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BV37" t="n">
         <v>14</v>
@@ -9960,7 +9960,7 @@
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G38" t="n">
         <v>1.81</v>
@@ -10019,7 +10019,7 @@
         <v>4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -10055,7 +10055,7 @@
         <v>2.22</v>
       </c>
       <c r="X38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="n">
         <v>21</v>
@@ -10064,7 +10064,7 @@
         <v>42</v>
       </c>
       <c r="AA38" t="n">
-        <v>890</v>
+        <v>690</v>
       </c>
       <c r="AB38" t="n">
         <v>11</v>
@@ -10079,7 +10079,7 @@
         <v>120</v>
       </c>
       <c r="AF38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG38" t="n">
         <v>10.5</v>
@@ -10103,7 +10103,7 @@
         <v>190</v>
       </c>
       <c r="AN38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO38" t="n">
         <v>55</v>
@@ -10115,13 +10115,13 @@
         <v>17.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AS38" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AT38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU38" t="n">
         <v>8.6</v>
@@ -10130,19 +10130,19 @@
         <v>17</v>
       </c>
       <c r="AW38" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX38" t="n">
         <v>10.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ38" t="n">
         <v>16</v>
       </c>
       <c r="BA38" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB38" t="n">
         <v>16.5</v>
@@ -10151,10 +10151,10 @@
         <v>15.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE38" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF38" t="n">
         <v>8</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10291,10 +10291,10 @@
         <v>1.54</v>
       </c>
       <c r="R39" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S39" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T39" t="n">
         <v>1.52</v>
@@ -10309,112 +10309,112 @@
         <v>1.6</v>
       </c>
       <c r="X39" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Y39" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Z39" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AA39" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB39" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AC39" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD39" t="n">
         <v>13.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AF39" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AG39" t="n">
         <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM39" t="n">
         <v>75</v>
       </c>
-      <c r="AJ39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>200</v>
-      </c>
       <c r="AN39" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AO39" t="n">
         <v>15</v>
       </c>
       <c r="AP39" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="AT39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY39" t="n">
         <v>10</v>
       </c>
       <c r="AZ39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BC39" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BF39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH39" t="n">
         <v>4.6</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10545,7 @@
         <v>1.65</v>
       </c>
       <c r="R40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S40" t="n">
         <v>2.62</v>
@@ -10611,7 +10611,7 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -10620,10 +10620,10 @@
         <v>21</v>
       </c>
       <c r="AQ40" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AR40" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AS40" t="n">
         <v>95</v>
@@ -10647,7 +10647,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA40" t="n">
         <v>44</v>
@@ -10659,7 +10659,7 @@
         <v>12.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE40" t="n">
         <v>70</v>
@@ -10692,7 +10692,7 @@
         <v>3.95</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BP40" t="n">
         <v>7.8</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10766,19 +10766,19 @@
         <v>1.4</v>
       </c>
       <c r="G41" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H41" t="n">
         <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J41" t="n">
         <v>4.9</v>
       </c>
       <c r="K41" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.28</v>
@@ -10865,7 +10865,7 @@
         <v>130</v>
       </c>
       <c r="AN41" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AO41" t="n">
         <v>150</v>
@@ -10877,10 +10877,10 @@
         <v>24</v>
       </c>
       <c r="AR41" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS41" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT41" t="n">
         <v>7.8</v>
@@ -10889,13 +10889,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX41" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY41" t="n">
         <v>8</v>
@@ -10904,7 +10904,7 @@
         <v>18</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB41" t="n">
         <v>9.6</v>
@@ -10913,16 +10913,16 @@
         <v>11.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF41" t="n">
         <v>4.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11035,10 +11035,10 @@
         <v>3.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N42" t="n">
         <v>2.16</v>
@@ -11047,22 +11047,22 @@
         <v>1.7</v>
       </c>
       <c r="P42" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="S42" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U42" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V42" t="n">
         <v>1.47</v>
@@ -11125,7 +11125,7 @@
         <v>180</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ42" t="n">
         <v>3.85</v>
@@ -11134,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AT42" t="n">
         <v>4.4</v>
@@ -11146,101 +11146,101 @@
         <v>8.4</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AY42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC42" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.55</v>
+        <v>3.25</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN42" t="n">
         <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11579,16 +11579,16 @@
         <v>2.5</v>
       </c>
       <c r="X44" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="Y44" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="Z44" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB44" t="n">
         <v>970</v>
@@ -11597,10 +11597,10 @@
         <v>17.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF44" t="n">
         <v>40</v>
@@ -11609,10 +11609,10 @@
         <v>36</v>
       </c>
       <c r="AH44" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ44" t="n">
         <v>970</v>
@@ -11621,7 +11621,7 @@
         <v>970</v>
       </c>
       <c r="AL44" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM44" t="n">
         <v>580</v>
@@ -11630,31 +11630,31 @@
         <v>15</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP44" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AS44" t="n">
         <v>2.5</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AX44" t="n">
         <v>8</v>
@@ -11663,28 +11663,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BC44" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG44" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="BH44" t="n">
         <v>3.95</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
         <v>3.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="R45" t="n">
         <v>1.94</v>
@@ -11905,7 +11905,7 @@
         <v>3.15</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="AW45" t="n">
         <v>2.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
         <v>3.15</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K46" t="n">
         <v>4.7</v>
@@ -12054,10 +12054,10 @@
         <v>1.2</v>
       </c>
       <c r="M46" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O46" t="n">
         <v>1.14</v>
@@ -12069,7 +12069,7 @@
         <v>1.44</v>
       </c>
       <c r="R46" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S46" t="n">
         <v>2.04</v>
@@ -12078,13 +12078,13 @@
         <v>1.45</v>
       </c>
       <c r="U46" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>1.47</v>
       </c>
       <c r="W46" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X46" t="n">
         <v>75</v>
@@ -12210,7 +12210,7 @@
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN46" t="n">
         <v>6.4</v>
@@ -12222,13 +12222,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR46" t="n">
         <v>22</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT46" t="n">
         <v>7.2</v>
@@ -12240,23 +12240,23 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ46" t="n">
         <v>13</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         <v>12</v>
       </c>
       <c r="AH47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI47" t="n">
         <v>46</v>
@@ -12404,7 +12404,7 @@
         <v>14.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT47" t="n">
         <v>9.800000000000001</v>
@@ -12428,7 +12428,7 @@
         <v>11.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB47" t="n">
         <v>17</v>
@@ -12440,7 +12440,7 @@
         <v>20</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF47" t="n">
         <v>8.199999999999999</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12604,7 @@
         <v>55</v>
       </c>
       <c r="AA48" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB48" t="n">
         <v>15.5</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
         <v>1.8</v>
       </c>
       <c r="G49" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H49" t="n">
         <v>4.9</v>
@@ -12807,7 +12807,7 @@
         <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K49" t="n">
         <v>3.75</v>
@@ -12846,16 +12846,16 @@
         <v>1.2</v>
       </c>
       <c r="W49" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X49" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z49" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA49" t="n">
         <v>900</v>
@@ -12864,22 +12864,22 @@
         <v>8</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE49" t="n">
         <v>110</v>
       </c>
       <c r="AF49" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG49" t="n">
         <v>11.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI49" t="n">
         <v>120</v>
@@ -12891,76 +12891,76 @@
         <v>26</v>
       </c>
       <c r="AL49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM49" t="n">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO49" t="n">
         <v>170</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX49" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AY49" t="n">
         <v>8</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA49" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC49" t="n">
         <v>20</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BH49" t="n">
         <v>2.98</v>
       </c>
       <c r="BI49" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="BJ49" t="n">
         <v>12.5</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
         <v>3.55</v>
@@ -13067,7 +13067,7 @@
         <v>3.15</v>
       </c>
       <c r="L50" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M50" t="n">
         <v>1.12</v>
@@ -13094,7 +13094,7 @@
         <v>2.1</v>
       </c>
       <c r="U50" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V50" t="n">
         <v>1.49</v>
@@ -13103,7 +13103,7 @@
         <v>1.39</v>
       </c>
       <c r="X50" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y50" t="n">
         <v>8.6</v>
@@ -13124,94 +13124,94 @@
         <v>970</v>
       </c>
       <c r="AE50" t="n">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="AF50" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AG50" t="n">
         <v>970</v>
       </c>
       <c r="AH50" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AI50" t="n">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AJ50" t="n">
         <v>900</v>
       </c>
       <c r="AK50" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="n">
-        <v>55</v>
+        <v>390</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AQ50" t="n">
         <v>5.7</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="AV50" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX50" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY50" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ50" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB50" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BF50" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BG50" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH50" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI50" t="n">
         <v>2.18</v>
@@ -13220,13 +13220,13 @@
         <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="BN50" t="n">
         <v>6.4</v>
@@ -13238,13 +13238,13 @@
         <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>38</v>
+        <v>4.6</v>
       </c>
       <c r="BT50" t="n">
         <v>5.8</v>
@@ -13256,23 +13256,23 @@
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13312,10 +13312,10 @@
         <v>1.93</v>
       </c>
       <c r="I51" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J51" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K51" t="n">
         <v>4.2</v>
@@ -13327,7 +13327,7 @@
         <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O51" t="n">
         <v>1.26</v>
@@ -13351,7 +13351,7 @@
         <v>2.18</v>
       </c>
       <c r="V51" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W51" t="n">
         <v>1.29</v>
@@ -13360,7 +13360,7 @@
         <v>22</v>
       </c>
       <c r="Y51" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="Z51" t="n">
         <v>16.5</v>
@@ -13381,34 +13381,34 @@
         <v>25</v>
       </c>
       <c r="AF51" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AG51" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AH51" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI51" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="n">
         <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AL51" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AM51" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN51" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AO51" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP51" t="n">
         <v>12.5</v>
@@ -13435,7 +13435,7 @@
         <v>14.5</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AY51" t="n">
         <v>12</v>
@@ -13444,22 +13444,22 @@
         <v>12.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG51" t="n">
         <v>10.5</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13599,7 @@
         <v>5.2</v>
       </c>
       <c r="T52" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U52" t="n">
         <v>1.67</v>
@@ -13611,112 +13611,112 @@
         <v>1.66</v>
       </c>
       <c r="X52" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="Y52" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Z52" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AA52" t="n">
         <v>900</v>
       </c>
       <c r="AB52" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD52" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF52" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AG52" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AH52" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ52" t="n">
         <v>900</v>
       </c>
       <c r="AK52" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM52" t="n">
         <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AO52" t="n">
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG52" t="n">
         <v>2.64</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>3.45</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         <v>3.7</v>
       </c>
       <c r="J53" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K53" t="n">
         <v>3.45</v>
@@ -13970,7 +13970,7 @@
         <v>6.8</v>
       </c>
       <c r="BG53" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BH53" t="n">
         <v>3.1</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -14065,13 +14065,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G54" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H54" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I54" t="n">
         <v>4.9</v>
@@ -14080,7 +14080,7 @@
         <v>3.5</v>
       </c>
       <c r="K54" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L54" t="n">
         <v>1.4</v>
@@ -14095,7 +14095,7 @@
         <v>1.41</v>
       </c>
       <c r="P54" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q54" t="n">
         <v>2.2</v>
@@ -14116,7 +14116,7 @@
         <v>1.25</v>
       </c>
       <c r="W54" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X54" t="n">
         <v>13</v>
@@ -14167,7 +14167,7 @@
         <v>150</v>
       </c>
       <c r="AN54" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO54" t="n">
         <v>110</v>
@@ -14194,7 +14194,7 @@
         <v>15.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX54" t="n">
         <v>9.800000000000001</v>
@@ -14206,7 +14206,7 @@
         <v>17.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB54" t="n">
         <v>19.5</v>
@@ -14224,7 +14224,7 @@
         <v>12.5</v>
       </c>
       <c r="BG54" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH54" t="n">
         <v>3.2</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -14322,16 +14322,16 @@
         <v>2.06</v>
       </c>
       <c r="G55" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K55" t="n">
         <v>3.4</v>
@@ -14343,34 +14343,34 @@
         <v>1.1</v>
       </c>
       <c r="N55" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O55" t="n">
         <v>1.46</v>
       </c>
       <c r="P55" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R55" t="n">
         <v>1.24</v>
       </c>
       <c r="S55" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T55" t="n">
         <v>2.04</v>
       </c>
       <c r="U55" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V55" t="n">
         <v>1.28</v>
       </c>
       <c r="W55" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X55" t="n">
         <v>12</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
         <v>1.3</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T56" t="n">
         <v>1.81</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
         <v>1.75</v>
       </c>
       <c r="I58" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J58" t="n">
         <v>3.85</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
         <v>1.82</v>
       </c>
       <c r="H59" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I59" t="n">
         <v>7.2</v>
@@ -15350,7 +15350,7 @@
         <v>3.35</v>
       </c>
       <c r="K59" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L59" t="n">
         <v>1.36</v>
@@ -15365,7 +15365,7 @@
         <v>1.32</v>
       </c>
       <c r="P59" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q59" t="n">
         <v>1.94</v>
@@ -15386,7 +15386,7 @@
         <v>1.18</v>
       </c>
       <c r="W59" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X59" t="n">
         <v>970</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -15598,13 +15598,13 @@
         <v>2.5</v>
       </c>
       <c r="I60" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J60" t="n">
         <v>3.2</v>
       </c>
       <c r="K60" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15613,13 +15613,13 @@
         <v>1.08</v>
       </c>
       <c r="N60" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
         <v>1.35</v>
       </c>
       <c r="P60" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q60" t="n">
         <v>2.02</v>
@@ -15637,7 +15637,7 @@
         <v>2.04</v>
       </c>
       <c r="V60" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W60" t="n">
         <v>1.44</v>
@@ -15694,61 +15694,61 @@
         <v>42</v>
       </c>
       <c r="AO60" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP60" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ60" t="n">
         <v>3.25</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW60" t="n">
         <v>4</v>
       </c>
-      <c r="AT60" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW60" t="n">
+      <c r="AX60" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG60" t="n">
         <v>3.9</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>3.85</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -15843,16 +15843,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G61" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H61" t="n">
         <v>2.32</v>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J61" t="n">
         <v>3.7</v>
@@ -15891,7 +15891,7 @@
         <v>2.42</v>
       </c>
       <c r="V61" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W61" t="n">
         <v>1.45</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
         <v>1.69</v>
       </c>
       <c r="P62" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q62" t="n">
         <v>3.05</v>
@@ -16142,7 +16142,7 @@
         <v>2.36</v>
       </c>
       <c r="U62" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V62" t="n">
         <v>1.27</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16366,7 @@
         <v>3.3</v>
       </c>
       <c r="K63" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -16387,7 +16387,7 @@
         <v>2.1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -16405,58 +16405,58 @@
         <v>1.28</v>
       </c>
       <c r="X63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA63" t="n">
         <v>900</v>
       </c>
       <c r="AB63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD63" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AE63" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ63" t="n">
         <v>900</v>
       </c>
       <c r="AK63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP63" t="n">
         <v>1.01</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
         <v>5.5</v>
       </c>
       <c r="I64" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J64" t="n">
         <v>4</v>
@@ -16644,7 +16644,7 @@
         <v>1.43</v>
       </c>
       <c r="S64" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T64" t="n">
         <v>1.8</v>
@@ -16656,10 +16656,10 @@
         <v>1.17</v>
       </c>
       <c r="W64" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X64" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y64" t="n">
         <v>27</v>
@@ -16719,10 +16719,10 @@
         <v>16</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT64" t="n">
         <v>7</v>
@@ -16734,7 +16734,7 @@
         <v>16.5</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX64" t="n">
         <v>7.8</v>
@@ -16746,7 +16746,7 @@
         <v>14.5</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB64" t="n">
         <v>11.5</v>
@@ -16755,16 +16755,16 @@
         <v>12</v>
       </c>
       <c r="BD64" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF64" t="n">
         <v>6.4</v>
       </c>
       <c r="BG64" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="BH64" t="n">
         <v>3.95</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -17113,67 +17113,67 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="G66" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="H66" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J66" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K66" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L66" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M66" t="n">
         <v>1.06</v>
       </c>
       <c r="N66" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O66" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P66" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R66" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S66" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T66" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U66" t="n">
         <v>2</v>
       </c>
       <c r="V66" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W66" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="X66" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y66" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA66" t="n">
         <v>900</v>
@@ -17182,16 +17182,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC66" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD66" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE66" t="n">
         <v>700</v>
       </c>
       <c r="AF66" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG66" t="n">
         <v>10.5</v>
@@ -17203,10 +17203,10 @@
         <v>700</v>
       </c>
       <c r="AJ66" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AK66" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL66" t="n">
         <v>40</v>
@@ -17215,7 +17215,7 @@
         <v>500</v>
       </c>
       <c r="AN66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO66" t="n">
         <v>700</v>
@@ -17227,22 +17227,22 @@
         <v>13.5</v>
       </c>
       <c r="AR66" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AS66" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT66" t="n">
         <v>6.8</v>
       </c>
       <c r="AU66" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV66" t="n">
         <v>15.5</v>
       </c>
       <c r="AW66" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX66" t="n">
         <v>8.4</v>
@@ -17254,7 +17254,7 @@
         <v>15</v>
       </c>
       <c r="BA66" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB66" t="n">
         <v>14.5</v>
@@ -17263,70 +17263,70 @@
         <v>14.5</v>
       </c>
       <c r="BD66" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE66" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF66" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BG66" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH66" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI66" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BJ66" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK66" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL66" t="n">
         <v>1000</v>
       </c>
       <c r="BM66" t="n">
-        <v>2.64</v>
+        <v>9.6</v>
       </c>
       <c r="BN66" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO66" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BP66" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ66" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR66" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS66" t="n">
         <v>7.4</v>
       </c>
       <c r="BT66" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BU66" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV66" t="n">
         <v>1000</v>
       </c>
       <c r="BW66" t="n">
-        <v>2.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX66" t="n">
         <v>1000</v>
       </c>
       <c r="BY66" t="n">
-        <v>2.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ66" t="n">
         <v>0</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -17370,34 +17370,34 @@
         <v>2.22</v>
       </c>
       <c r="G67" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H67" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K67" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L67" t="n">
         <v>1.55</v>
       </c>
       <c r="M67" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N67" t="n">
         <v>2.46</v>
       </c>
       <c r="O67" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P67" t="n">
         <v>1.51</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.52</v>
       </c>
       <c r="Q67" t="n">
         <v>2.52</v>
@@ -17418,7 +17418,7 @@
         <v>1.3</v>
       </c>
       <c r="W67" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X67" t="n">
         <v>970</v>
@@ -17436,7 +17436,7 @@
         <v>970</v>
       </c>
       <c r="AC67" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD67" t="n">
         <v>500</v>
@@ -17472,7 +17472,7 @@
         <v>500</v>
       </c>
       <c r="AO67" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP67" t="n">
         <v>6.4</v>
@@ -17481,52 +17481,52 @@
         <v>7.8</v>
       </c>
       <c r="AR67" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS67" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT67" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU67" t="n">
         <v>5.4</v>
       </c>
       <c r="AV67" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX67" t="n">
         <v>3.9</v>
       </c>
-      <c r="AW67" t="n">
+      <c r="AY67" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB67" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX67" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA67" t="n">
+      <c r="BC67" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB67" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD67" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE67" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF67" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG67" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH67" t="n">
         <v>1000</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -17636,7 +17636,7 @@
         <v>3.05</v>
       </c>
       <c r="K68" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L68" t="n">
         <v>1.46</v>
@@ -17666,7 +17666,7 @@
         <v>2.08</v>
       </c>
       <c r="U68" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V68" t="n">
         <v>1.31</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -17875,37 +17875,37 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I69" t="n">
         <v>4.5</v>
       </c>
       <c r="J69" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K69" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L69" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M69" t="n">
         <v>1.07</v>
       </c>
       <c r="N69" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O69" t="n">
         <v>1.32</v>
       </c>
       <c r="P69" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q69" t="n">
         <v>1.94</v>
@@ -17920,19 +17920,19 @@
         <v>1.79</v>
       </c>
       <c r="U69" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V69" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W69" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="X69" t="n">
         <v>16</v>
       </c>
       <c r="Y69" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z69" t="n">
         <v>32</v>
@@ -17941,7 +17941,7 @@
         <v>90</v>
       </c>
       <c r="AB69" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC69" t="n">
         <v>8.6</v>
@@ -17965,10 +17965,10 @@
         <v>60</v>
       </c>
       <c r="AJ69" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL69" t="n">
         <v>38</v>
@@ -17977,19 +17977,19 @@
         <v>120</v>
       </c>
       <c r="AN69" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO69" t="n">
         <v>60</v>
       </c>
       <c r="AP69" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ69" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR69" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS69" t="n">
         <v>1.03</v>
@@ -18001,19 +18001,19 @@
         <v>1.03</v>
       </c>
       <c r="AV69" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW69" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AW69" t="n">
-        <v>32</v>
       </c>
       <c r="AX69" t="n">
         <v>1.03</v>
       </c>
       <c r="AY69" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ69" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA69" t="n">
         <v>1.03</v>
@@ -18025,7 +18025,7 @@
         <v>1.03</v>
       </c>
       <c r="BD69" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BE69" t="n">
         <v>1.03</v>
@@ -18034,19 +18034,19 @@
         <v>13</v>
       </c>
       <c r="BG69" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH69" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI69" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ69" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK69" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
@@ -18055,50 +18055,50 @@
         <v>1.01</v>
       </c>
       <c r="BN69" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO69" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ69" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR69" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT69" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU69" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV69" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW69" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BX69" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY69" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BZ69" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CA69" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -18129,22 +18129,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="G70" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="H70" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I70" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J70" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K70" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L70" t="n">
         <v>1.32</v>
@@ -18153,58 +18153,58 @@
         <v>1.06</v>
       </c>
       <c r="N70" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O70" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P70" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R70" t="n">
         <v>1.38</v>
       </c>
       <c r="S70" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T70" t="n">
         <v>1.92</v>
       </c>
       <c r="U70" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V70" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W70" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="X70" t="n">
         <v>18</v>
       </c>
       <c r="Y70" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z70" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA70" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AB70" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC70" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD70" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE70" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF70" t="n">
         <v>10.5</v>
@@ -18213,10 +18213,10 @@
         <v>12</v>
       </c>
       <c r="AH70" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI70" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ70" t="n">
         <v>18.5</v>
@@ -18228,13 +18228,13 @@
         <v>42</v>
       </c>
       <c r="AM70" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN70" t="n">
         <v>10.5</v>
       </c>
       <c r="AO70" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP70" t="n">
         <v>12.5</v>
@@ -18261,10 +18261,10 @@
         <v>1.03</v>
       </c>
       <c r="AX70" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY70" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ70" t="n">
         <v>17.5</v>
@@ -18285,16 +18285,16 @@
         <v>1.03</v>
       </c>
       <c r="BF70" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG70" t="n">
         <v>90</v>
       </c>
       <c r="BH70" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI70" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ70" t="n">
         <v>11</v>
@@ -18309,16 +18309,16 @@
         <v>1.01</v>
       </c>
       <c r="BN70" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO70" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP70" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ70" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR70" t="n">
         <v>1000</v>
@@ -18327,32 +18327,32 @@
         <v>19</v>
       </c>
       <c r="BT70" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU70" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BX70" t="n">
         <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BZ70" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA70" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G71" t="n">
         <v>2.76</v>
       </c>
       <c r="H71" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
         <v>3.4</v>
@@ -18548,7 +18548,7 @@
         <v>3.1</v>
       </c>
       <c r="BI71" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="BJ71" t="n">
         <v>10.5</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -18655,7 +18655,7 @@
         <v>4.8</v>
       </c>
       <c r="L72" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M72" t="n">
         <v>1.07</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -18891,22 +18891,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G73" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I73" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K73" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L73" t="n">
         <v>1.49</v>
@@ -18918,7 +18918,7 @@
         <v>2.62</v>
       </c>
       <c r="O73" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P73" t="n">
         <v>1.53</v>
@@ -18930,46 +18930,46 @@
         <v>1.19</v>
       </c>
       <c r="S73" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T73" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U73" t="n">
         <v>1.78</v>
       </c>
       <c r="V73" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W73" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X73" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y73" t="n">
         <v>12</v>
       </c>
       <c r="Z73" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA73" t="n">
         <v>120</v>
       </c>
       <c r="AB73" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC73" t="n">
         <v>7.6</v>
       </c>
       <c r="AD73" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE73" t="n">
         <v>75</v>
       </c>
       <c r="AF73" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG73" t="n">
         <v>12</v>
@@ -18999,28 +18999,28 @@
         <v>120</v>
       </c>
       <c r="AP73" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ73" t="n">
         <v>9.6</v>
       </c>
       <c r="AR73" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AS73" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT73" t="n">
         <v>5.7</v>
       </c>
       <c r="AU73" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV73" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW73" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX73" t="n">
         <v>10.5</v>
@@ -19041,22 +19041,22 @@
         <v>25</v>
       </c>
       <c r="BD73" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE73" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF73" t="n">
         <v>19</v>
       </c>
       <c r="BG73" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH73" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI73" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ73" t="n">
         <v>12</v>
@@ -19068,7 +19068,7 @@
         <v>1000</v>
       </c>
       <c r="BM73" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="BN73" t="n">
         <v>4.9</v>
@@ -19083,10 +19083,10 @@
         <v>7</v>
       </c>
       <c r="BR73" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS73" t="n">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="BT73" t="n">
         <v>7.6</v>
@@ -19098,13 +19098,13 @@
         <v>44</v>
       </c>
       <c r="BW73" t="n">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="BX73" t="n">
         <v>65</v>
       </c>
       <c r="BY73" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="BZ73" t="n">
         <v>0</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G74" t="n">
         <v>1.66</v>
@@ -19301,7 +19301,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF74" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG74" t="n">
         <v>8.199999999999999</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
